--- a/chatbot/hoja/pestanas_bot_itswood.xlsx
+++ b/chatbot/hoja/pestanas_bot_itswood.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_ERRORES" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_COTIZACIONES" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROVEEDORES" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CATALOGO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CONFIG" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CATALOGO" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49309,6 +49310,6368 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C2021"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>clave</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="3" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="3" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="3" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="3" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="3" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="3" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="3" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="3" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="3" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="3" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="3" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="3" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="3" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="3" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="3" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="3" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="3" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="3" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="3" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="3" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="3" t="n"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="3" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="3" t="n"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="3" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="3" t="n"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="3" t="n"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="3" t="n"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="3" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="3" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="3" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="3" t="n"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="3" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="3" t="n"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="3" t="n"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="3" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="3" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="3" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="3" t="n"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="3" t="n"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="3" t="n"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="3" t="n"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="3" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="3" t="n"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="3" t="n"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="3" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="3" t="n"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="3" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="3" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="3" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="3" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="3" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="3" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="3" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="3" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="3" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="3" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="3" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="3" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="3" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="3" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="3" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="3" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="3" t="n"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="3" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="3" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="3" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="3" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="3" t="n"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="3" t="n"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="3" t="n"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="3" t="n"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="3" t="n"/>
+    </row>
+    <row r="165">
+      <c r="B165" s="3" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="3" t="n"/>
+    </row>
+    <row r="167">
+      <c r="B167" s="3" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="3" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="3" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="3" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="3" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="3" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="3" t="n"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="3" t="n"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="3" t="n"/>
+    </row>
+    <row r="176">
+      <c r="B176" s="3" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="3" t="n"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="3" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="3" t="n"/>
+    </row>
+    <row r="180">
+      <c r="B180" s="3" t="n"/>
+    </row>
+    <row r="181">
+      <c r="B181" s="3" t="n"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="3" t="n"/>
+    </row>
+    <row r="183">
+      <c r="B183" s="3" t="n"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="3" t="n"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="3" t="n"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="3" t="n"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="3" t="n"/>
+    </row>
+    <row r="188">
+      <c r="B188" s="3" t="n"/>
+    </row>
+    <row r="189">
+      <c r="B189" s="3" t="n"/>
+    </row>
+    <row r="190">
+      <c r="B190" s="3" t="n"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="3" t="n"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="3" t="n"/>
+    </row>
+    <row r="193">
+      <c r="B193" s="3" t="n"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="3" t="n"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="3" t="n"/>
+    </row>
+    <row r="196">
+      <c r="B196" s="3" t="n"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="3" t="n"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="3" t="n"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="3" t="n"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="3" t="n"/>
+    </row>
+    <row r="201">
+      <c r="B201" s="3" t="n"/>
+    </row>
+    <row r="202">
+      <c r="B202" s="3" t="n"/>
+    </row>
+    <row r="203">
+      <c r="B203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="B204" s="3" t="n"/>
+    </row>
+    <row r="205">
+      <c r="B205" s="3" t="n"/>
+    </row>
+    <row r="206">
+      <c r="B206" s="3" t="n"/>
+    </row>
+    <row r="207">
+      <c r="B207" s="3" t="n"/>
+    </row>
+    <row r="208">
+      <c r="B208" s="3" t="n"/>
+    </row>
+    <row r="209">
+      <c r="B209" s="3" t="n"/>
+    </row>
+    <row r="210">
+      <c r="B210" s="3" t="n"/>
+    </row>
+    <row r="211">
+      <c r="B211" s="3" t="n"/>
+    </row>
+    <row r="212">
+      <c r="B212" s="3" t="n"/>
+    </row>
+    <row r="213">
+      <c r="B213" s="3" t="n"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="3" t="n"/>
+    </row>
+    <row r="215">
+      <c r="B215" s="3" t="n"/>
+    </row>
+    <row r="216">
+      <c r="B216" s="3" t="n"/>
+    </row>
+    <row r="217">
+      <c r="B217" s="3" t="n"/>
+    </row>
+    <row r="218">
+      <c r="B218" s="3" t="n"/>
+    </row>
+    <row r="219">
+      <c r="B219" s="3" t="n"/>
+    </row>
+    <row r="220">
+      <c r="B220" s="3" t="n"/>
+    </row>
+    <row r="221">
+      <c r="B221" s="3" t="n"/>
+    </row>
+    <row r="222">
+      <c r="B222" s="3" t="n"/>
+    </row>
+    <row r="223">
+      <c r="B223" s="3" t="n"/>
+    </row>
+    <row r="224">
+      <c r="B224" s="3" t="n"/>
+    </row>
+    <row r="225">
+      <c r="B225" s="3" t="n"/>
+    </row>
+    <row r="226">
+      <c r="B226" s="3" t="n"/>
+    </row>
+    <row r="227">
+      <c r="B227" s="3" t="n"/>
+    </row>
+    <row r="228">
+      <c r="B228" s="3" t="n"/>
+    </row>
+    <row r="229">
+      <c r="B229" s="3" t="n"/>
+    </row>
+    <row r="230">
+      <c r="B230" s="3" t="n"/>
+    </row>
+    <row r="231">
+      <c r="B231" s="3" t="n"/>
+    </row>
+    <row r="232">
+      <c r="B232" s="3" t="n"/>
+    </row>
+    <row r="233">
+      <c r="B233" s="3" t="n"/>
+    </row>
+    <row r="234">
+      <c r="B234" s="3" t="n"/>
+    </row>
+    <row r="235">
+      <c r="B235" s="3" t="n"/>
+    </row>
+    <row r="236">
+      <c r="B236" s="3" t="n"/>
+    </row>
+    <row r="237">
+      <c r="B237" s="3" t="n"/>
+    </row>
+    <row r="238">
+      <c r="B238" s="3" t="n"/>
+    </row>
+    <row r="239">
+      <c r="B239" s="3" t="n"/>
+    </row>
+    <row r="240">
+      <c r="B240" s="3" t="n"/>
+    </row>
+    <row r="241">
+      <c r="B241" s="3" t="n"/>
+    </row>
+    <row r="242">
+      <c r="B242" s="3" t="n"/>
+    </row>
+    <row r="243">
+      <c r="B243" s="3" t="n"/>
+    </row>
+    <row r="244">
+      <c r="B244" s="3" t="n"/>
+    </row>
+    <row r="245">
+      <c r="B245" s="3" t="n"/>
+    </row>
+    <row r="246">
+      <c r="B246" s="3" t="n"/>
+    </row>
+    <row r="247">
+      <c r="B247" s="3" t="n"/>
+    </row>
+    <row r="248">
+      <c r="B248" s="3" t="n"/>
+    </row>
+    <row r="249">
+      <c r="B249" s="3" t="n"/>
+    </row>
+    <row r="250">
+      <c r="B250" s="3" t="n"/>
+    </row>
+    <row r="251">
+      <c r="B251" s="3" t="n"/>
+    </row>
+    <row r="252">
+      <c r="B252" s="3" t="n"/>
+    </row>
+    <row r="253">
+      <c r="B253" s="3" t="n"/>
+    </row>
+    <row r="254">
+      <c r="B254" s="3" t="n"/>
+    </row>
+    <row r="255">
+      <c r="B255" s="3" t="n"/>
+    </row>
+    <row r="256">
+      <c r="B256" s="3" t="n"/>
+    </row>
+    <row r="257">
+      <c r="B257" s="3" t="n"/>
+    </row>
+    <row r="258">
+      <c r="B258" s="3" t="n"/>
+    </row>
+    <row r="259">
+      <c r="B259" s="3" t="n"/>
+    </row>
+    <row r="260">
+      <c r="B260" s="3" t="n"/>
+    </row>
+    <row r="261">
+      <c r="B261" s="3" t="n"/>
+    </row>
+    <row r="262">
+      <c r="B262" s="3" t="n"/>
+    </row>
+    <row r="263">
+      <c r="B263" s="3" t="n"/>
+    </row>
+    <row r="264">
+      <c r="B264" s="3" t="n"/>
+    </row>
+    <row r="265">
+      <c r="B265" s="3" t="n"/>
+    </row>
+    <row r="266">
+      <c r="B266" s="3" t="n"/>
+    </row>
+    <row r="267">
+      <c r="B267" s="3" t="n"/>
+    </row>
+    <row r="268">
+      <c r="B268" s="3" t="n"/>
+    </row>
+    <row r="269">
+      <c r="B269" s="3" t="n"/>
+    </row>
+    <row r="270">
+      <c r="B270" s="3" t="n"/>
+    </row>
+    <row r="271">
+      <c r="B271" s="3" t="n"/>
+    </row>
+    <row r="272">
+      <c r="B272" s="3" t="n"/>
+    </row>
+    <row r="273">
+      <c r="B273" s="3" t="n"/>
+    </row>
+    <row r="274">
+      <c r="B274" s="3" t="n"/>
+    </row>
+    <row r="275">
+      <c r="B275" s="3" t="n"/>
+    </row>
+    <row r="276">
+      <c r="B276" s="3" t="n"/>
+    </row>
+    <row r="277">
+      <c r="B277" s="3" t="n"/>
+    </row>
+    <row r="278">
+      <c r="B278" s="3" t="n"/>
+    </row>
+    <row r="279">
+      <c r="B279" s="3" t="n"/>
+    </row>
+    <row r="280">
+      <c r="B280" s="3" t="n"/>
+    </row>
+    <row r="281">
+      <c r="B281" s="3" t="n"/>
+    </row>
+    <row r="282">
+      <c r="B282" s="3" t="n"/>
+    </row>
+    <row r="283">
+      <c r="B283" s="3" t="n"/>
+    </row>
+    <row r="284">
+      <c r="B284" s="3" t="n"/>
+    </row>
+    <row r="285">
+      <c r="B285" s="3" t="n"/>
+    </row>
+    <row r="286">
+      <c r="B286" s="3" t="n"/>
+    </row>
+    <row r="287">
+      <c r="B287" s="3" t="n"/>
+    </row>
+    <row r="288">
+      <c r="B288" s="3" t="n"/>
+    </row>
+    <row r="289">
+      <c r="B289" s="3" t="n"/>
+    </row>
+    <row r="290">
+      <c r="B290" s="3" t="n"/>
+    </row>
+    <row r="291">
+      <c r="B291" s="3" t="n"/>
+    </row>
+    <row r="292">
+      <c r="B292" s="3" t="n"/>
+    </row>
+    <row r="293">
+      <c r="B293" s="3" t="n"/>
+    </row>
+    <row r="294">
+      <c r="B294" s="3" t="n"/>
+    </row>
+    <row r="295">
+      <c r="B295" s="3" t="n"/>
+    </row>
+    <row r="296">
+      <c r="B296" s="3" t="n"/>
+    </row>
+    <row r="297">
+      <c r="B297" s="3" t="n"/>
+    </row>
+    <row r="298">
+      <c r="B298" s="3" t="n"/>
+    </row>
+    <row r="299">
+      <c r="B299" s="3" t="n"/>
+    </row>
+    <row r="300">
+      <c r="B300" s="3" t="n"/>
+    </row>
+    <row r="301">
+      <c r="B301" s="3" t="n"/>
+    </row>
+    <row r="302">
+      <c r="B302" s="3" t="n"/>
+    </row>
+    <row r="303">
+      <c r="B303" s="3" t="n"/>
+    </row>
+    <row r="304">
+      <c r="B304" s="3" t="n"/>
+    </row>
+    <row r="305">
+      <c r="B305" s="3" t="n"/>
+    </row>
+    <row r="306">
+      <c r="B306" s="3" t="n"/>
+    </row>
+    <row r="307">
+      <c r="B307" s="3" t="n"/>
+    </row>
+    <row r="308">
+      <c r="B308" s="3" t="n"/>
+    </row>
+    <row r="309">
+      <c r="B309" s="3" t="n"/>
+    </row>
+    <row r="310">
+      <c r="B310" s="3" t="n"/>
+    </row>
+    <row r="311">
+      <c r="B311" s="3" t="n"/>
+    </row>
+    <row r="312">
+      <c r="B312" s="3" t="n"/>
+    </row>
+    <row r="313">
+      <c r="B313" s="3" t="n"/>
+    </row>
+    <row r="314">
+      <c r="B314" s="3" t="n"/>
+    </row>
+    <row r="315">
+      <c r="B315" s="3" t="n"/>
+    </row>
+    <row r="316">
+      <c r="B316" s="3" t="n"/>
+    </row>
+    <row r="317">
+      <c r="B317" s="3" t="n"/>
+    </row>
+    <row r="318">
+      <c r="B318" s="3" t="n"/>
+    </row>
+    <row r="319">
+      <c r="B319" s="3" t="n"/>
+    </row>
+    <row r="320">
+      <c r="B320" s="3" t="n"/>
+    </row>
+    <row r="321">
+      <c r="B321" s="3" t="n"/>
+    </row>
+    <row r="322">
+      <c r="B322" s="3" t="n"/>
+    </row>
+    <row r="323">
+      <c r="B323" s="3" t="n"/>
+    </row>
+    <row r="324">
+      <c r="B324" s="3" t="n"/>
+    </row>
+    <row r="325">
+      <c r="B325" s="3" t="n"/>
+    </row>
+    <row r="326">
+      <c r="B326" s="3" t="n"/>
+    </row>
+    <row r="327">
+      <c r="B327" s="3" t="n"/>
+    </row>
+    <row r="328">
+      <c r="B328" s="3" t="n"/>
+    </row>
+    <row r="329">
+      <c r="B329" s="3" t="n"/>
+    </row>
+    <row r="330">
+      <c r="B330" s="3" t="n"/>
+    </row>
+    <row r="331">
+      <c r="B331" s="3" t="n"/>
+    </row>
+    <row r="332">
+      <c r="B332" s="3" t="n"/>
+    </row>
+    <row r="333">
+      <c r="B333" s="3" t="n"/>
+    </row>
+    <row r="334">
+      <c r="B334" s="3" t="n"/>
+    </row>
+    <row r="335">
+      <c r="B335" s="3" t="n"/>
+    </row>
+    <row r="336">
+      <c r="B336" s="3" t="n"/>
+    </row>
+    <row r="337">
+      <c r="B337" s="3" t="n"/>
+    </row>
+    <row r="338">
+      <c r="B338" s="3" t="n"/>
+    </row>
+    <row r="339">
+      <c r="B339" s="3" t="n"/>
+    </row>
+    <row r="340">
+      <c r="B340" s="3" t="n"/>
+    </row>
+    <row r="341">
+      <c r="B341" s="3" t="n"/>
+    </row>
+    <row r="342">
+      <c r="B342" s="3" t="n"/>
+    </row>
+    <row r="343">
+      <c r="B343" s="3" t="n"/>
+    </row>
+    <row r="344">
+      <c r="B344" s="3" t="n"/>
+    </row>
+    <row r="345">
+      <c r="B345" s="3" t="n"/>
+    </row>
+    <row r="346">
+      <c r="B346" s="3" t="n"/>
+    </row>
+    <row r="347">
+      <c r="B347" s="3" t="n"/>
+    </row>
+    <row r="348">
+      <c r="B348" s="3" t="n"/>
+    </row>
+    <row r="349">
+      <c r="B349" s="3" t="n"/>
+    </row>
+    <row r="350">
+      <c r="B350" s="3" t="n"/>
+    </row>
+    <row r="351">
+      <c r="B351" s="3" t="n"/>
+    </row>
+    <row r="352">
+      <c r="B352" s="3" t="n"/>
+    </row>
+    <row r="353">
+      <c r="B353" s="3" t="n"/>
+    </row>
+    <row r="354">
+      <c r="B354" s="3" t="n"/>
+    </row>
+    <row r="355">
+      <c r="B355" s="3" t="n"/>
+    </row>
+    <row r="356">
+      <c r="B356" s="3" t="n"/>
+    </row>
+    <row r="357">
+      <c r="B357" s="3" t="n"/>
+    </row>
+    <row r="358">
+      <c r="B358" s="3" t="n"/>
+    </row>
+    <row r="359">
+      <c r="B359" s="3" t="n"/>
+    </row>
+    <row r="360">
+      <c r="B360" s="3" t="n"/>
+    </row>
+    <row r="361">
+      <c r="B361" s="3" t="n"/>
+    </row>
+    <row r="362">
+      <c r="B362" s="3" t="n"/>
+    </row>
+    <row r="363">
+      <c r="B363" s="3" t="n"/>
+    </row>
+    <row r="364">
+      <c r="B364" s="3" t="n"/>
+    </row>
+    <row r="365">
+      <c r="B365" s="3" t="n"/>
+    </row>
+    <row r="366">
+      <c r="B366" s="3" t="n"/>
+    </row>
+    <row r="367">
+      <c r="B367" s="3" t="n"/>
+    </row>
+    <row r="368">
+      <c r="B368" s="3" t="n"/>
+    </row>
+    <row r="369">
+      <c r="B369" s="3" t="n"/>
+    </row>
+    <row r="370">
+      <c r="B370" s="3" t="n"/>
+    </row>
+    <row r="371">
+      <c r="B371" s="3" t="n"/>
+    </row>
+    <row r="372">
+      <c r="B372" s="3" t="n"/>
+    </row>
+    <row r="373">
+      <c r="B373" s="3" t="n"/>
+    </row>
+    <row r="374">
+      <c r="B374" s="3" t="n"/>
+    </row>
+    <row r="375">
+      <c r="B375" s="3" t="n"/>
+    </row>
+    <row r="376">
+      <c r="B376" s="3" t="n"/>
+    </row>
+    <row r="377">
+      <c r="B377" s="3" t="n"/>
+    </row>
+    <row r="378">
+      <c r="B378" s="3" t="n"/>
+    </row>
+    <row r="379">
+      <c r="B379" s="3" t="n"/>
+    </row>
+    <row r="380">
+      <c r="B380" s="3" t="n"/>
+    </row>
+    <row r="381">
+      <c r="B381" s="3" t="n"/>
+    </row>
+    <row r="382">
+      <c r="B382" s="3" t="n"/>
+    </row>
+    <row r="383">
+      <c r="B383" s="3" t="n"/>
+    </row>
+    <row r="384">
+      <c r="B384" s="3" t="n"/>
+    </row>
+    <row r="385">
+      <c r="B385" s="3" t="n"/>
+    </row>
+    <row r="386">
+      <c r="B386" s="3" t="n"/>
+    </row>
+    <row r="387">
+      <c r="B387" s="3" t="n"/>
+    </row>
+    <row r="388">
+      <c r="B388" s="3" t="n"/>
+    </row>
+    <row r="389">
+      <c r="B389" s="3" t="n"/>
+    </row>
+    <row r="390">
+      <c r="B390" s="3" t="n"/>
+    </row>
+    <row r="391">
+      <c r="B391" s="3" t="n"/>
+    </row>
+    <row r="392">
+      <c r="B392" s="3" t="n"/>
+    </row>
+    <row r="393">
+      <c r="B393" s="3" t="n"/>
+    </row>
+    <row r="394">
+      <c r="B394" s="3" t="n"/>
+    </row>
+    <row r="395">
+      <c r="B395" s="3" t="n"/>
+    </row>
+    <row r="396">
+      <c r="B396" s="3" t="n"/>
+    </row>
+    <row r="397">
+      <c r="B397" s="3" t="n"/>
+    </row>
+    <row r="398">
+      <c r="B398" s="3" t="n"/>
+    </row>
+    <row r="399">
+      <c r="B399" s="3" t="n"/>
+    </row>
+    <row r="400">
+      <c r="B400" s="3" t="n"/>
+    </row>
+    <row r="401">
+      <c r="B401" s="3" t="n"/>
+    </row>
+    <row r="402">
+      <c r="B402" s="3" t="n"/>
+    </row>
+    <row r="403">
+      <c r="B403" s="3" t="n"/>
+    </row>
+    <row r="404">
+      <c r="B404" s="3" t="n"/>
+    </row>
+    <row r="405">
+      <c r="B405" s="3" t="n"/>
+    </row>
+    <row r="406">
+      <c r="B406" s="3" t="n"/>
+    </row>
+    <row r="407">
+      <c r="B407" s="3" t="n"/>
+    </row>
+    <row r="408">
+      <c r="B408" s="3" t="n"/>
+    </row>
+    <row r="409">
+      <c r="B409" s="3" t="n"/>
+    </row>
+    <row r="410">
+      <c r="B410" s="3" t="n"/>
+    </row>
+    <row r="411">
+      <c r="B411" s="3" t="n"/>
+    </row>
+    <row r="412">
+      <c r="B412" s="3" t="n"/>
+    </row>
+    <row r="413">
+      <c r="B413" s="3" t="n"/>
+    </row>
+    <row r="414">
+      <c r="B414" s="3" t="n"/>
+    </row>
+    <row r="415">
+      <c r="B415" s="3" t="n"/>
+    </row>
+    <row r="416">
+      <c r="B416" s="3" t="n"/>
+    </row>
+    <row r="417">
+      <c r="B417" s="3" t="n"/>
+    </row>
+    <row r="418">
+      <c r="B418" s="3" t="n"/>
+    </row>
+    <row r="419">
+      <c r="B419" s="3" t="n"/>
+    </row>
+    <row r="420">
+      <c r="B420" s="3" t="n"/>
+    </row>
+    <row r="421">
+      <c r="B421" s="3" t="n"/>
+    </row>
+    <row r="422">
+      <c r="B422" s="3" t="n"/>
+    </row>
+    <row r="423">
+      <c r="B423" s="3" t="n"/>
+    </row>
+    <row r="424">
+      <c r="B424" s="3" t="n"/>
+    </row>
+    <row r="425">
+      <c r="B425" s="3" t="n"/>
+    </row>
+    <row r="426">
+      <c r="B426" s="3" t="n"/>
+    </row>
+    <row r="427">
+      <c r="B427" s="3" t="n"/>
+    </row>
+    <row r="428">
+      <c r="B428" s="3" t="n"/>
+    </row>
+    <row r="429">
+      <c r="B429" s="3" t="n"/>
+    </row>
+    <row r="430">
+      <c r="B430" s="3" t="n"/>
+    </row>
+    <row r="431">
+      <c r="B431" s="3" t="n"/>
+    </row>
+    <row r="432">
+      <c r="B432" s="3" t="n"/>
+    </row>
+    <row r="433">
+      <c r="B433" s="3" t="n"/>
+    </row>
+    <row r="434">
+      <c r="B434" s="3" t="n"/>
+    </row>
+    <row r="435">
+      <c r="B435" s="3" t="n"/>
+    </row>
+    <row r="436">
+      <c r="B436" s="3" t="n"/>
+    </row>
+    <row r="437">
+      <c r="B437" s="3" t="n"/>
+    </row>
+    <row r="438">
+      <c r="B438" s="3" t="n"/>
+    </row>
+    <row r="439">
+      <c r="B439" s="3" t="n"/>
+    </row>
+    <row r="440">
+      <c r="B440" s="3" t="n"/>
+    </row>
+    <row r="441">
+      <c r="B441" s="3" t="n"/>
+    </row>
+    <row r="442">
+      <c r="B442" s="3" t="n"/>
+    </row>
+    <row r="443">
+      <c r="B443" s="3" t="n"/>
+    </row>
+    <row r="444">
+      <c r="B444" s="3" t="n"/>
+    </row>
+    <row r="445">
+      <c r="B445" s="3" t="n"/>
+    </row>
+    <row r="446">
+      <c r="B446" s="3" t="n"/>
+    </row>
+    <row r="447">
+      <c r="B447" s="3" t="n"/>
+    </row>
+    <row r="448">
+      <c r="B448" s="3" t="n"/>
+    </row>
+    <row r="449">
+      <c r="B449" s="3" t="n"/>
+    </row>
+    <row r="450">
+      <c r="B450" s="3" t="n"/>
+    </row>
+    <row r="451">
+      <c r="B451" s="3" t="n"/>
+    </row>
+    <row r="452">
+      <c r="B452" s="3" t="n"/>
+    </row>
+    <row r="453">
+      <c r="B453" s="3" t="n"/>
+    </row>
+    <row r="454">
+      <c r="B454" s="3" t="n"/>
+    </row>
+    <row r="455">
+      <c r="B455" s="3" t="n"/>
+    </row>
+    <row r="456">
+      <c r="B456" s="3" t="n"/>
+    </row>
+    <row r="457">
+      <c r="B457" s="3" t="n"/>
+    </row>
+    <row r="458">
+      <c r="B458" s="3" t="n"/>
+    </row>
+    <row r="459">
+      <c r="B459" s="3" t="n"/>
+    </row>
+    <row r="460">
+      <c r="B460" s="3" t="n"/>
+    </row>
+    <row r="461">
+      <c r="B461" s="3" t="n"/>
+    </row>
+    <row r="462">
+      <c r="B462" s="3" t="n"/>
+    </row>
+    <row r="463">
+      <c r="B463" s="3" t="n"/>
+    </row>
+    <row r="464">
+      <c r="B464" s="3" t="n"/>
+    </row>
+    <row r="465">
+      <c r="B465" s="3" t="n"/>
+    </row>
+    <row r="466">
+      <c r="B466" s="3" t="n"/>
+    </row>
+    <row r="467">
+      <c r="B467" s="3" t="n"/>
+    </row>
+    <row r="468">
+      <c r="B468" s="3" t="n"/>
+    </row>
+    <row r="469">
+      <c r="B469" s="3" t="n"/>
+    </row>
+    <row r="470">
+      <c r="B470" s="3" t="n"/>
+    </row>
+    <row r="471">
+      <c r="B471" s="3" t="n"/>
+    </row>
+    <row r="472">
+      <c r="B472" s="3" t="n"/>
+    </row>
+    <row r="473">
+      <c r="B473" s="3" t="n"/>
+    </row>
+    <row r="474">
+      <c r="B474" s="3" t="n"/>
+    </row>
+    <row r="475">
+      <c r="B475" s="3" t="n"/>
+    </row>
+    <row r="476">
+      <c r="B476" s="3" t="n"/>
+    </row>
+    <row r="477">
+      <c r="B477" s="3" t="n"/>
+    </row>
+    <row r="478">
+      <c r="B478" s="3" t="n"/>
+    </row>
+    <row r="479">
+      <c r="B479" s="3" t="n"/>
+    </row>
+    <row r="480">
+      <c r="B480" s="3" t="n"/>
+    </row>
+    <row r="481">
+      <c r="B481" s="3" t="n"/>
+    </row>
+    <row r="482">
+      <c r="B482" s="3" t="n"/>
+    </row>
+    <row r="483">
+      <c r="B483" s="3" t="n"/>
+    </row>
+    <row r="484">
+      <c r="B484" s="3" t="n"/>
+    </row>
+    <row r="485">
+      <c r="B485" s="3" t="n"/>
+    </row>
+    <row r="486">
+      <c r="B486" s="3" t="n"/>
+    </row>
+    <row r="487">
+      <c r="B487" s="3" t="n"/>
+    </row>
+    <row r="488">
+      <c r="B488" s="3" t="n"/>
+    </row>
+    <row r="489">
+      <c r="B489" s="3" t="n"/>
+    </row>
+    <row r="490">
+      <c r="B490" s="3" t="n"/>
+    </row>
+    <row r="491">
+      <c r="B491" s="3" t="n"/>
+    </row>
+    <row r="492">
+      <c r="B492" s="3" t="n"/>
+    </row>
+    <row r="493">
+      <c r="B493" s="3" t="n"/>
+    </row>
+    <row r="494">
+      <c r="B494" s="3" t="n"/>
+    </row>
+    <row r="495">
+      <c r="B495" s="3" t="n"/>
+    </row>
+    <row r="496">
+      <c r="B496" s="3" t="n"/>
+    </row>
+    <row r="497">
+      <c r="B497" s="3" t="n"/>
+    </row>
+    <row r="498">
+      <c r="B498" s="3" t="n"/>
+    </row>
+    <row r="499">
+      <c r="B499" s="3" t="n"/>
+    </row>
+    <row r="500">
+      <c r="B500" s="3" t="n"/>
+    </row>
+    <row r="501">
+      <c r="B501" s="3" t="n"/>
+    </row>
+    <row r="502">
+      <c r="B502" s="3" t="n"/>
+    </row>
+    <row r="503">
+      <c r="B503" s="3" t="n"/>
+    </row>
+    <row r="504">
+      <c r="B504" s="3" t="n"/>
+    </row>
+    <row r="505">
+      <c r="B505" s="3" t="n"/>
+    </row>
+    <row r="506">
+      <c r="B506" s="3" t="n"/>
+    </row>
+    <row r="507">
+      <c r="B507" s="3" t="n"/>
+    </row>
+    <row r="508">
+      <c r="B508" s="3" t="n"/>
+    </row>
+    <row r="509">
+      <c r="B509" s="3" t="n"/>
+    </row>
+    <row r="510">
+      <c r="B510" s="3" t="n"/>
+    </row>
+    <row r="511">
+      <c r="B511" s="3" t="n"/>
+    </row>
+    <row r="512">
+      <c r="B512" s="3" t="n"/>
+    </row>
+    <row r="513">
+      <c r="B513" s="3" t="n"/>
+    </row>
+    <row r="514">
+      <c r="B514" s="3" t="n"/>
+    </row>
+    <row r="515">
+      <c r="B515" s="3" t="n"/>
+    </row>
+    <row r="516">
+      <c r="B516" s="3" t="n"/>
+    </row>
+    <row r="517">
+      <c r="B517" s="3" t="n"/>
+    </row>
+    <row r="518">
+      <c r="B518" s="3" t="n"/>
+    </row>
+    <row r="519">
+      <c r="B519" s="3" t="n"/>
+    </row>
+    <row r="520">
+      <c r="B520" s="3" t="n"/>
+    </row>
+    <row r="521">
+      <c r="B521" s="3" t="n"/>
+    </row>
+    <row r="522">
+      <c r="B522" s="3" t="n"/>
+    </row>
+    <row r="523">
+      <c r="B523" s="3" t="n"/>
+    </row>
+    <row r="524">
+      <c r="B524" s="3" t="n"/>
+    </row>
+    <row r="525">
+      <c r="B525" s="3" t="n"/>
+    </row>
+    <row r="526">
+      <c r="B526" s="3" t="n"/>
+    </row>
+    <row r="527">
+      <c r="B527" s="3" t="n"/>
+    </row>
+    <row r="528">
+      <c r="B528" s="3" t="n"/>
+    </row>
+    <row r="529">
+      <c r="B529" s="3" t="n"/>
+    </row>
+    <row r="530">
+      <c r="B530" s="3" t="n"/>
+    </row>
+    <row r="531">
+      <c r="B531" s="3" t="n"/>
+    </row>
+    <row r="532">
+      <c r="B532" s="3" t="n"/>
+    </row>
+    <row r="533">
+      <c r="B533" s="3" t="n"/>
+    </row>
+    <row r="534">
+      <c r="B534" s="3" t="n"/>
+    </row>
+    <row r="535">
+      <c r="B535" s="3" t="n"/>
+    </row>
+    <row r="536">
+      <c r="B536" s="3" t="n"/>
+    </row>
+    <row r="537">
+      <c r="B537" s="3" t="n"/>
+    </row>
+    <row r="538">
+      <c r="B538" s="3" t="n"/>
+    </row>
+    <row r="539">
+      <c r="B539" s="3" t="n"/>
+    </row>
+    <row r="540">
+      <c r="B540" s="3" t="n"/>
+    </row>
+    <row r="541">
+      <c r="B541" s="3" t="n"/>
+    </row>
+    <row r="542">
+      <c r="B542" s="3" t="n"/>
+    </row>
+    <row r="543">
+      <c r="B543" s="3" t="n"/>
+    </row>
+    <row r="544">
+      <c r="B544" s="3" t="n"/>
+    </row>
+    <row r="545">
+      <c r="B545" s="3" t="n"/>
+    </row>
+    <row r="546">
+      <c r="B546" s="3" t="n"/>
+    </row>
+    <row r="547">
+      <c r="B547" s="3" t="n"/>
+    </row>
+    <row r="548">
+      <c r="B548" s="3" t="n"/>
+    </row>
+    <row r="549">
+      <c r="B549" s="3" t="n"/>
+    </row>
+    <row r="550">
+      <c r="B550" s="3" t="n"/>
+    </row>
+    <row r="551">
+      <c r="B551" s="3" t="n"/>
+    </row>
+    <row r="552">
+      <c r="B552" s="3" t="n"/>
+    </row>
+    <row r="553">
+      <c r="B553" s="3" t="n"/>
+    </row>
+    <row r="554">
+      <c r="B554" s="3" t="n"/>
+    </row>
+    <row r="555">
+      <c r="B555" s="3" t="n"/>
+    </row>
+    <row r="556">
+      <c r="B556" s="3" t="n"/>
+    </row>
+    <row r="557">
+      <c r="B557" s="3" t="n"/>
+    </row>
+    <row r="558">
+      <c r="B558" s="3" t="n"/>
+    </row>
+    <row r="559">
+      <c r="B559" s="3" t="n"/>
+    </row>
+    <row r="560">
+      <c r="B560" s="3" t="n"/>
+    </row>
+    <row r="561">
+      <c r="B561" s="3" t="n"/>
+    </row>
+    <row r="562">
+      <c r="B562" s="3" t="n"/>
+    </row>
+    <row r="563">
+      <c r="B563" s="3" t="n"/>
+    </row>
+    <row r="564">
+      <c r="B564" s="3" t="n"/>
+    </row>
+    <row r="565">
+      <c r="B565" s="3" t="n"/>
+    </row>
+    <row r="566">
+      <c r="B566" s="3" t="n"/>
+    </row>
+    <row r="567">
+      <c r="B567" s="3" t="n"/>
+    </row>
+    <row r="568">
+      <c r="B568" s="3" t="n"/>
+    </row>
+    <row r="569">
+      <c r="B569" s="3" t="n"/>
+    </row>
+    <row r="570">
+      <c r="B570" s="3" t="n"/>
+    </row>
+    <row r="571">
+      <c r="B571" s="3" t="n"/>
+    </row>
+    <row r="572">
+      <c r="B572" s="3" t="n"/>
+    </row>
+    <row r="573">
+      <c r="B573" s="3" t="n"/>
+    </row>
+    <row r="574">
+      <c r="B574" s="3" t="n"/>
+    </row>
+    <row r="575">
+      <c r="B575" s="3" t="n"/>
+    </row>
+    <row r="576">
+      <c r="B576" s="3" t="n"/>
+    </row>
+    <row r="577">
+      <c r="B577" s="3" t="n"/>
+    </row>
+    <row r="578">
+      <c r="B578" s="3" t="n"/>
+    </row>
+    <row r="579">
+      <c r="B579" s="3" t="n"/>
+    </row>
+    <row r="580">
+      <c r="B580" s="3" t="n"/>
+    </row>
+    <row r="581">
+      <c r="B581" s="3" t="n"/>
+    </row>
+    <row r="582">
+      <c r="B582" s="3" t="n"/>
+    </row>
+    <row r="583">
+      <c r="B583" s="3" t="n"/>
+    </row>
+    <row r="584">
+      <c r="B584" s="3" t="n"/>
+    </row>
+    <row r="585">
+      <c r="B585" s="3" t="n"/>
+    </row>
+    <row r="586">
+      <c r="B586" s="3" t="n"/>
+    </row>
+    <row r="587">
+      <c r="B587" s="3" t="n"/>
+    </row>
+    <row r="588">
+      <c r="B588" s="3" t="n"/>
+    </row>
+    <row r="589">
+      <c r="B589" s="3" t="n"/>
+    </row>
+    <row r="590">
+      <c r="B590" s="3" t="n"/>
+    </row>
+    <row r="591">
+      <c r="B591" s="3" t="n"/>
+    </row>
+    <row r="592">
+      <c r="B592" s="3" t="n"/>
+    </row>
+    <row r="593">
+      <c r="B593" s="3" t="n"/>
+    </row>
+    <row r="594">
+      <c r="B594" s="3" t="n"/>
+    </row>
+    <row r="595">
+      <c r="B595" s="3" t="n"/>
+    </row>
+    <row r="596">
+      <c r="B596" s="3" t="n"/>
+    </row>
+    <row r="597">
+      <c r="B597" s="3" t="n"/>
+    </row>
+    <row r="598">
+      <c r="B598" s="3" t="n"/>
+    </row>
+    <row r="599">
+      <c r="B599" s="3" t="n"/>
+    </row>
+    <row r="600">
+      <c r="B600" s="3" t="n"/>
+    </row>
+    <row r="601">
+      <c r="B601" s="3" t="n"/>
+    </row>
+    <row r="602">
+      <c r="B602" s="3" t="n"/>
+    </row>
+    <row r="603">
+      <c r="B603" s="3" t="n"/>
+    </row>
+    <row r="604">
+      <c r="B604" s="3" t="n"/>
+    </row>
+    <row r="605">
+      <c r="B605" s="3" t="n"/>
+    </row>
+    <row r="606">
+      <c r="B606" s="3" t="n"/>
+    </row>
+    <row r="607">
+      <c r="B607" s="3" t="n"/>
+    </row>
+    <row r="608">
+      <c r="B608" s="3" t="n"/>
+    </row>
+    <row r="609">
+      <c r="B609" s="3" t="n"/>
+    </row>
+    <row r="610">
+      <c r="B610" s="3" t="n"/>
+    </row>
+    <row r="611">
+      <c r="B611" s="3" t="n"/>
+    </row>
+    <row r="612">
+      <c r="B612" s="3" t="n"/>
+    </row>
+    <row r="613">
+      <c r="B613" s="3" t="n"/>
+    </row>
+    <row r="614">
+      <c r="B614" s="3" t="n"/>
+    </row>
+    <row r="615">
+      <c r="B615" s="3" t="n"/>
+    </row>
+    <row r="616">
+      <c r="B616" s="3" t="n"/>
+    </row>
+    <row r="617">
+      <c r="B617" s="3" t="n"/>
+    </row>
+    <row r="618">
+      <c r="B618" s="3" t="n"/>
+    </row>
+    <row r="619">
+      <c r="B619" s="3" t="n"/>
+    </row>
+    <row r="620">
+      <c r="B620" s="3" t="n"/>
+    </row>
+    <row r="621">
+      <c r="B621" s="3" t="n"/>
+    </row>
+    <row r="622">
+      <c r="B622" s="3" t="n"/>
+    </row>
+    <row r="623">
+      <c r="B623" s="3" t="n"/>
+    </row>
+    <row r="624">
+      <c r="B624" s="3" t="n"/>
+    </row>
+    <row r="625">
+      <c r="B625" s="3" t="n"/>
+    </row>
+    <row r="626">
+      <c r="B626" s="3" t="n"/>
+    </row>
+    <row r="627">
+      <c r="B627" s="3" t="n"/>
+    </row>
+    <row r="628">
+      <c r="B628" s="3" t="n"/>
+    </row>
+    <row r="629">
+      <c r="B629" s="3" t="n"/>
+    </row>
+    <row r="630">
+      <c r="B630" s="3" t="n"/>
+    </row>
+    <row r="631">
+      <c r="B631" s="3" t="n"/>
+    </row>
+    <row r="632">
+      <c r="B632" s="3" t="n"/>
+    </row>
+    <row r="633">
+      <c r="B633" s="3" t="n"/>
+    </row>
+    <row r="634">
+      <c r="B634" s="3" t="n"/>
+    </row>
+    <row r="635">
+      <c r="B635" s="3" t="n"/>
+    </row>
+    <row r="636">
+      <c r="B636" s="3" t="n"/>
+    </row>
+    <row r="637">
+      <c r="B637" s="3" t="n"/>
+    </row>
+    <row r="638">
+      <c r="B638" s="3" t="n"/>
+    </row>
+    <row r="639">
+      <c r="B639" s="3" t="n"/>
+    </row>
+    <row r="640">
+      <c r="B640" s="3" t="n"/>
+    </row>
+    <row r="641">
+      <c r="B641" s="3" t="n"/>
+    </row>
+    <row r="642">
+      <c r="B642" s="3" t="n"/>
+    </row>
+    <row r="643">
+      <c r="B643" s="3" t="n"/>
+    </row>
+    <row r="644">
+      <c r="B644" s="3" t="n"/>
+    </row>
+    <row r="645">
+      <c r="B645" s="3" t="n"/>
+    </row>
+    <row r="646">
+      <c r="B646" s="3" t="n"/>
+    </row>
+    <row r="647">
+      <c r="B647" s="3" t="n"/>
+    </row>
+    <row r="648">
+      <c r="B648" s="3" t="n"/>
+    </row>
+    <row r="649">
+      <c r="B649" s="3" t="n"/>
+    </row>
+    <row r="650">
+      <c r="B650" s="3" t="n"/>
+    </row>
+    <row r="651">
+      <c r="B651" s="3" t="n"/>
+    </row>
+    <row r="652">
+      <c r="B652" s="3" t="n"/>
+    </row>
+    <row r="653">
+      <c r="B653" s="3" t="n"/>
+    </row>
+    <row r="654">
+      <c r="B654" s="3" t="n"/>
+    </row>
+    <row r="655">
+      <c r="B655" s="3" t="n"/>
+    </row>
+    <row r="656">
+      <c r="B656" s="3" t="n"/>
+    </row>
+    <row r="657">
+      <c r="B657" s="3" t="n"/>
+    </row>
+    <row r="658">
+      <c r="B658" s="3" t="n"/>
+    </row>
+    <row r="659">
+      <c r="B659" s="3" t="n"/>
+    </row>
+    <row r="660">
+      <c r="B660" s="3" t="n"/>
+    </row>
+    <row r="661">
+      <c r="B661" s="3" t="n"/>
+    </row>
+    <row r="662">
+      <c r="B662" s="3" t="n"/>
+    </row>
+    <row r="663">
+      <c r="B663" s="3" t="n"/>
+    </row>
+    <row r="664">
+      <c r="B664" s="3" t="n"/>
+    </row>
+    <row r="665">
+      <c r="B665" s="3" t="n"/>
+    </row>
+    <row r="666">
+      <c r="B666" s="3" t="n"/>
+    </row>
+    <row r="667">
+      <c r="B667" s="3" t="n"/>
+    </row>
+    <row r="668">
+      <c r="B668" s="3" t="n"/>
+    </row>
+    <row r="669">
+      <c r="B669" s="3" t="n"/>
+    </row>
+    <row r="670">
+      <c r="B670" s="3" t="n"/>
+    </row>
+    <row r="671">
+      <c r="B671" s="3" t="n"/>
+    </row>
+    <row r="672">
+      <c r="B672" s="3" t="n"/>
+    </row>
+    <row r="673">
+      <c r="B673" s="3" t="n"/>
+    </row>
+    <row r="674">
+      <c r="B674" s="3" t="n"/>
+    </row>
+    <row r="675">
+      <c r="B675" s="3" t="n"/>
+    </row>
+    <row r="676">
+      <c r="B676" s="3" t="n"/>
+    </row>
+    <row r="677">
+      <c r="B677" s="3" t="n"/>
+    </row>
+    <row r="678">
+      <c r="B678" s="3" t="n"/>
+    </row>
+    <row r="679">
+      <c r="B679" s="3" t="n"/>
+    </row>
+    <row r="680">
+      <c r="B680" s="3" t="n"/>
+    </row>
+    <row r="681">
+      <c r="B681" s="3" t="n"/>
+    </row>
+    <row r="682">
+      <c r="B682" s="3" t="n"/>
+    </row>
+    <row r="683">
+      <c r="B683" s="3" t="n"/>
+    </row>
+    <row r="684">
+      <c r="B684" s="3" t="n"/>
+    </row>
+    <row r="685">
+      <c r="B685" s="3" t="n"/>
+    </row>
+    <row r="686">
+      <c r="B686" s="3" t="n"/>
+    </row>
+    <row r="687">
+      <c r="B687" s="3" t="n"/>
+    </row>
+    <row r="688">
+      <c r="B688" s="3" t="n"/>
+    </row>
+    <row r="689">
+      <c r="B689" s="3" t="n"/>
+    </row>
+    <row r="690">
+      <c r="B690" s="3" t="n"/>
+    </row>
+    <row r="691">
+      <c r="B691" s="3" t="n"/>
+    </row>
+    <row r="692">
+      <c r="B692" s="3" t="n"/>
+    </row>
+    <row r="693">
+      <c r="B693" s="3" t="n"/>
+    </row>
+    <row r="694">
+      <c r="B694" s="3" t="n"/>
+    </row>
+    <row r="695">
+      <c r="B695" s="3" t="n"/>
+    </row>
+    <row r="696">
+      <c r="B696" s="3" t="n"/>
+    </row>
+    <row r="697">
+      <c r="B697" s="3" t="n"/>
+    </row>
+    <row r="698">
+      <c r="B698" s="3" t="n"/>
+    </row>
+    <row r="699">
+      <c r="B699" s="3" t="n"/>
+    </row>
+    <row r="700">
+      <c r="B700" s="3" t="n"/>
+    </row>
+    <row r="701">
+      <c r="B701" s="3" t="n"/>
+    </row>
+    <row r="702">
+      <c r="B702" s="3" t="n"/>
+    </row>
+    <row r="703">
+      <c r="B703" s="3" t="n"/>
+    </row>
+    <row r="704">
+      <c r="B704" s="3" t="n"/>
+    </row>
+    <row r="705">
+      <c r="B705" s="3" t="n"/>
+    </row>
+    <row r="706">
+      <c r="B706" s="3" t="n"/>
+    </row>
+    <row r="707">
+      <c r="B707" s="3" t="n"/>
+    </row>
+    <row r="708">
+      <c r="B708" s="3" t="n"/>
+    </row>
+    <row r="709">
+      <c r="B709" s="3" t="n"/>
+    </row>
+    <row r="710">
+      <c r="B710" s="3" t="n"/>
+    </row>
+    <row r="711">
+      <c r="B711" s="3" t="n"/>
+    </row>
+    <row r="712">
+      <c r="B712" s="3" t="n"/>
+    </row>
+    <row r="713">
+      <c r="B713" s="3" t="n"/>
+    </row>
+    <row r="714">
+      <c r="B714" s="3" t="n"/>
+    </row>
+    <row r="715">
+      <c r="B715" s="3" t="n"/>
+    </row>
+    <row r="716">
+      <c r="B716" s="3" t="n"/>
+    </row>
+    <row r="717">
+      <c r="B717" s="3" t="n"/>
+    </row>
+    <row r="718">
+      <c r="B718" s="3" t="n"/>
+    </row>
+    <row r="719">
+      <c r="B719" s="3" t="n"/>
+    </row>
+    <row r="720">
+      <c r="B720" s="3" t="n"/>
+    </row>
+    <row r="721">
+      <c r="B721" s="3" t="n"/>
+    </row>
+    <row r="722">
+      <c r="B722" s="3" t="n"/>
+    </row>
+    <row r="723">
+      <c r="B723" s="3" t="n"/>
+    </row>
+    <row r="724">
+      <c r="B724" s="3" t="n"/>
+    </row>
+    <row r="725">
+      <c r="B725" s="3" t="n"/>
+    </row>
+    <row r="726">
+      <c r="B726" s="3" t="n"/>
+    </row>
+    <row r="727">
+      <c r="B727" s="3" t="n"/>
+    </row>
+    <row r="728">
+      <c r="B728" s="3" t="n"/>
+    </row>
+    <row r="729">
+      <c r="B729" s="3" t="n"/>
+    </row>
+    <row r="730">
+      <c r="B730" s="3" t="n"/>
+    </row>
+    <row r="731">
+      <c r="B731" s="3" t="n"/>
+    </row>
+    <row r="732">
+      <c r="B732" s="3" t="n"/>
+    </row>
+    <row r="733">
+      <c r="B733" s="3" t="n"/>
+    </row>
+    <row r="734">
+      <c r="B734" s="3" t="n"/>
+    </row>
+    <row r="735">
+      <c r="B735" s="3" t="n"/>
+    </row>
+    <row r="736">
+      <c r="B736" s="3" t="n"/>
+    </row>
+    <row r="737">
+      <c r="B737" s="3" t="n"/>
+    </row>
+    <row r="738">
+      <c r="B738" s="3" t="n"/>
+    </row>
+    <row r="739">
+      <c r="B739" s="3" t="n"/>
+    </row>
+    <row r="740">
+      <c r="B740" s="3" t="n"/>
+    </row>
+    <row r="741">
+      <c r="B741" s="3" t="n"/>
+    </row>
+    <row r="742">
+      <c r="B742" s="3" t="n"/>
+    </row>
+    <row r="743">
+      <c r="B743" s="3" t="n"/>
+    </row>
+    <row r="744">
+      <c r="B744" s="3" t="n"/>
+    </row>
+    <row r="745">
+      <c r="B745" s="3" t="n"/>
+    </row>
+    <row r="746">
+      <c r="B746" s="3" t="n"/>
+    </row>
+    <row r="747">
+      <c r="B747" s="3" t="n"/>
+    </row>
+    <row r="748">
+      <c r="B748" s="3" t="n"/>
+    </row>
+    <row r="749">
+      <c r="B749" s="3" t="n"/>
+    </row>
+    <row r="750">
+      <c r="B750" s="3" t="n"/>
+    </row>
+    <row r="751">
+      <c r="B751" s="3" t="n"/>
+    </row>
+    <row r="752">
+      <c r="B752" s="3" t="n"/>
+    </row>
+    <row r="753">
+      <c r="B753" s="3" t="n"/>
+    </row>
+    <row r="754">
+      <c r="B754" s="3" t="n"/>
+    </row>
+    <row r="755">
+      <c r="B755" s="3" t="n"/>
+    </row>
+    <row r="756">
+      <c r="B756" s="3" t="n"/>
+    </row>
+    <row r="757">
+      <c r="B757" s="3" t="n"/>
+    </row>
+    <row r="758">
+      <c r="B758" s="3" t="n"/>
+    </row>
+    <row r="759">
+      <c r="B759" s="3" t="n"/>
+    </row>
+    <row r="760">
+      <c r="B760" s="3" t="n"/>
+    </row>
+    <row r="761">
+      <c r="B761" s="3" t="n"/>
+    </row>
+    <row r="762">
+      <c r="B762" s="3" t="n"/>
+    </row>
+    <row r="763">
+      <c r="B763" s="3" t="n"/>
+    </row>
+    <row r="764">
+      <c r="B764" s="3" t="n"/>
+    </row>
+    <row r="765">
+      <c r="B765" s="3" t="n"/>
+    </row>
+    <row r="766">
+      <c r="B766" s="3" t="n"/>
+    </row>
+    <row r="767">
+      <c r="B767" s="3" t="n"/>
+    </row>
+    <row r="768">
+      <c r="B768" s="3" t="n"/>
+    </row>
+    <row r="769">
+      <c r="B769" s="3" t="n"/>
+    </row>
+    <row r="770">
+      <c r="B770" s="3" t="n"/>
+    </row>
+    <row r="771">
+      <c r="B771" s="3" t="n"/>
+    </row>
+    <row r="772">
+      <c r="B772" s="3" t="n"/>
+    </row>
+    <row r="773">
+      <c r="B773" s="3" t="n"/>
+    </row>
+    <row r="774">
+      <c r="B774" s="3" t="n"/>
+    </row>
+    <row r="775">
+      <c r="B775" s="3" t="n"/>
+    </row>
+    <row r="776">
+      <c r="B776" s="3" t="n"/>
+    </row>
+    <row r="777">
+      <c r="B777" s="3" t="n"/>
+    </row>
+    <row r="778">
+      <c r="B778" s="3" t="n"/>
+    </row>
+    <row r="779">
+      <c r="B779" s="3" t="n"/>
+    </row>
+    <row r="780">
+      <c r="B780" s="3" t="n"/>
+    </row>
+    <row r="781">
+      <c r="B781" s="3" t="n"/>
+    </row>
+    <row r="782">
+      <c r="B782" s="3" t="n"/>
+    </row>
+    <row r="783">
+      <c r="B783" s="3" t="n"/>
+    </row>
+    <row r="784">
+      <c r="B784" s="3" t="n"/>
+    </row>
+    <row r="785">
+      <c r="B785" s="3" t="n"/>
+    </row>
+    <row r="786">
+      <c r="B786" s="3" t="n"/>
+    </row>
+    <row r="787">
+      <c r="B787" s="3" t="n"/>
+    </row>
+    <row r="788">
+      <c r="B788" s="3" t="n"/>
+    </row>
+    <row r="789">
+      <c r="B789" s="3" t="n"/>
+    </row>
+    <row r="790">
+      <c r="B790" s="3" t="n"/>
+    </row>
+    <row r="791">
+      <c r="B791" s="3" t="n"/>
+    </row>
+    <row r="792">
+      <c r="B792" s="3" t="n"/>
+    </row>
+    <row r="793">
+      <c r="B793" s="3" t="n"/>
+    </row>
+    <row r="794">
+      <c r="B794" s="3" t="n"/>
+    </row>
+    <row r="795">
+      <c r="B795" s="3" t="n"/>
+    </row>
+    <row r="796">
+      <c r="B796" s="3" t="n"/>
+    </row>
+    <row r="797">
+      <c r="B797" s="3" t="n"/>
+    </row>
+    <row r="798">
+      <c r="B798" s="3" t="n"/>
+    </row>
+    <row r="799">
+      <c r="B799" s="3" t="n"/>
+    </row>
+    <row r="800">
+      <c r="B800" s="3" t="n"/>
+    </row>
+    <row r="801">
+      <c r="B801" s="3" t="n"/>
+    </row>
+    <row r="802">
+      <c r="B802" s="3" t="n"/>
+    </row>
+    <row r="803">
+      <c r="B803" s="3" t="n"/>
+    </row>
+    <row r="804">
+      <c r="B804" s="3" t="n"/>
+    </row>
+    <row r="805">
+      <c r="B805" s="3" t="n"/>
+    </row>
+    <row r="806">
+      <c r="B806" s="3" t="n"/>
+    </row>
+    <row r="807">
+      <c r="B807" s="3" t="n"/>
+    </row>
+    <row r="808">
+      <c r="B808" s="3" t="n"/>
+    </row>
+    <row r="809">
+      <c r="B809" s="3" t="n"/>
+    </row>
+    <row r="810">
+      <c r="B810" s="3" t="n"/>
+    </row>
+    <row r="811">
+      <c r="B811" s="3" t="n"/>
+    </row>
+    <row r="812">
+      <c r="B812" s="3" t="n"/>
+    </row>
+    <row r="813">
+      <c r="B813" s="3" t="n"/>
+    </row>
+    <row r="814">
+      <c r="B814" s="3" t="n"/>
+    </row>
+    <row r="815">
+      <c r="B815" s="3" t="n"/>
+    </row>
+    <row r="816">
+      <c r="B816" s="3" t="n"/>
+    </row>
+    <row r="817">
+      <c r="B817" s="3" t="n"/>
+    </row>
+    <row r="818">
+      <c r="B818" s="3" t="n"/>
+    </row>
+    <row r="819">
+      <c r="B819" s="3" t="n"/>
+    </row>
+    <row r="820">
+      <c r="B820" s="3" t="n"/>
+    </row>
+    <row r="821">
+      <c r="B821" s="3" t="n"/>
+    </row>
+    <row r="822">
+      <c r="B822" s="3" t="n"/>
+    </row>
+    <row r="823">
+      <c r="B823" s="3" t="n"/>
+    </row>
+    <row r="824">
+      <c r="B824" s="3" t="n"/>
+    </row>
+    <row r="825">
+      <c r="B825" s="3" t="n"/>
+    </row>
+    <row r="826">
+      <c r="B826" s="3" t="n"/>
+    </row>
+    <row r="827">
+      <c r="B827" s="3" t="n"/>
+    </row>
+    <row r="828">
+      <c r="B828" s="3" t="n"/>
+    </row>
+    <row r="829">
+      <c r="B829" s="3" t="n"/>
+    </row>
+    <row r="830">
+      <c r="B830" s="3" t="n"/>
+    </row>
+    <row r="831">
+      <c r="B831" s="3" t="n"/>
+    </row>
+    <row r="832">
+      <c r="B832" s="3" t="n"/>
+    </row>
+    <row r="833">
+      <c r="B833" s="3" t="n"/>
+    </row>
+    <row r="834">
+      <c r="B834" s="3" t="n"/>
+    </row>
+    <row r="835">
+      <c r="B835" s="3" t="n"/>
+    </row>
+    <row r="836">
+      <c r="B836" s="3" t="n"/>
+    </row>
+    <row r="837">
+      <c r="B837" s="3" t="n"/>
+    </row>
+    <row r="838">
+      <c r="B838" s="3" t="n"/>
+    </row>
+    <row r="839">
+      <c r="B839" s="3" t="n"/>
+    </row>
+    <row r="840">
+      <c r="B840" s="3" t="n"/>
+    </row>
+    <row r="841">
+      <c r="B841" s="3" t="n"/>
+    </row>
+    <row r="842">
+      <c r="B842" s="3" t="n"/>
+    </row>
+    <row r="843">
+      <c r="B843" s="3" t="n"/>
+    </row>
+    <row r="844">
+      <c r="B844" s="3" t="n"/>
+    </row>
+    <row r="845">
+      <c r="B845" s="3" t="n"/>
+    </row>
+    <row r="846">
+      <c r="B846" s="3" t="n"/>
+    </row>
+    <row r="847">
+      <c r="B847" s="3" t="n"/>
+    </row>
+    <row r="848">
+      <c r="B848" s="3" t="n"/>
+    </row>
+    <row r="849">
+      <c r="B849" s="3" t="n"/>
+    </row>
+    <row r="850">
+      <c r="B850" s="3" t="n"/>
+    </row>
+    <row r="851">
+      <c r="B851" s="3" t="n"/>
+    </row>
+    <row r="852">
+      <c r="B852" s="3" t="n"/>
+    </row>
+    <row r="853">
+      <c r="B853" s="3" t="n"/>
+    </row>
+    <row r="854">
+      <c r="B854" s="3" t="n"/>
+    </row>
+    <row r="855">
+      <c r="B855" s="3" t="n"/>
+    </row>
+    <row r="856">
+      <c r="B856" s="3" t="n"/>
+    </row>
+    <row r="857">
+      <c r="B857" s="3" t="n"/>
+    </row>
+    <row r="858">
+      <c r="B858" s="3" t="n"/>
+    </row>
+    <row r="859">
+      <c r="B859" s="3" t="n"/>
+    </row>
+    <row r="860">
+      <c r="B860" s="3" t="n"/>
+    </row>
+    <row r="861">
+      <c r="B861" s="3" t="n"/>
+    </row>
+    <row r="862">
+      <c r="B862" s="3" t="n"/>
+    </row>
+    <row r="863">
+      <c r="B863" s="3" t="n"/>
+    </row>
+    <row r="864">
+      <c r="B864" s="3" t="n"/>
+    </row>
+    <row r="865">
+      <c r="B865" s="3" t="n"/>
+    </row>
+    <row r="866">
+      <c r="B866" s="3" t="n"/>
+    </row>
+    <row r="867">
+      <c r="B867" s="3" t="n"/>
+    </row>
+    <row r="868">
+      <c r="B868" s="3" t="n"/>
+    </row>
+    <row r="869">
+      <c r="B869" s="3" t="n"/>
+    </row>
+    <row r="870">
+      <c r="B870" s="3" t="n"/>
+    </row>
+    <row r="871">
+      <c r="B871" s="3" t="n"/>
+    </row>
+    <row r="872">
+      <c r="B872" s="3" t="n"/>
+    </row>
+    <row r="873">
+      <c r="B873" s="3" t="n"/>
+    </row>
+    <row r="874">
+      <c r="B874" s="3" t="n"/>
+    </row>
+    <row r="875">
+      <c r="B875" s="3" t="n"/>
+    </row>
+    <row r="876">
+      <c r="B876" s="3" t="n"/>
+    </row>
+    <row r="877">
+      <c r="B877" s="3" t="n"/>
+    </row>
+    <row r="878">
+      <c r="B878" s="3" t="n"/>
+    </row>
+    <row r="879">
+      <c r="B879" s="3" t="n"/>
+    </row>
+    <row r="880">
+      <c r="B880" s="3" t="n"/>
+    </row>
+    <row r="881">
+      <c r="B881" s="3" t="n"/>
+    </row>
+    <row r="882">
+      <c r="B882" s="3" t="n"/>
+    </row>
+    <row r="883">
+      <c r="B883" s="3" t="n"/>
+    </row>
+    <row r="884">
+      <c r="B884" s="3" t="n"/>
+    </row>
+    <row r="885">
+      <c r="B885" s="3" t="n"/>
+    </row>
+    <row r="886">
+      <c r="B886" s="3" t="n"/>
+    </row>
+    <row r="887">
+      <c r="B887" s="3" t="n"/>
+    </row>
+    <row r="888">
+      <c r="B888" s="3" t="n"/>
+    </row>
+    <row r="889">
+      <c r="B889" s="3" t="n"/>
+    </row>
+    <row r="890">
+      <c r="B890" s="3" t="n"/>
+    </row>
+    <row r="891">
+      <c r="B891" s="3" t="n"/>
+    </row>
+    <row r="892">
+      <c r="B892" s="3" t="n"/>
+    </row>
+    <row r="893">
+      <c r="B893" s="3" t="n"/>
+    </row>
+    <row r="894">
+      <c r="B894" s="3" t="n"/>
+    </row>
+    <row r="895">
+      <c r="B895" s="3" t="n"/>
+    </row>
+    <row r="896">
+      <c r="B896" s="3" t="n"/>
+    </row>
+    <row r="897">
+      <c r="B897" s="3" t="n"/>
+    </row>
+    <row r="898">
+      <c r="B898" s="3" t="n"/>
+    </row>
+    <row r="899">
+      <c r="B899" s="3" t="n"/>
+    </row>
+    <row r="900">
+      <c r="B900" s="3" t="n"/>
+    </row>
+    <row r="901">
+      <c r="B901" s="3" t="n"/>
+    </row>
+    <row r="902">
+      <c r="B902" s="3" t="n"/>
+    </row>
+    <row r="903">
+      <c r="B903" s="3" t="n"/>
+    </row>
+    <row r="904">
+      <c r="B904" s="3" t="n"/>
+    </row>
+    <row r="905">
+      <c r="B905" s="3" t="n"/>
+    </row>
+    <row r="906">
+      <c r="B906" s="3" t="n"/>
+    </row>
+    <row r="907">
+      <c r="B907" s="3" t="n"/>
+    </row>
+    <row r="908">
+      <c r="B908" s="3" t="n"/>
+    </row>
+    <row r="909">
+      <c r="B909" s="3" t="n"/>
+    </row>
+    <row r="910">
+      <c r="B910" s="3" t="n"/>
+    </row>
+    <row r="911">
+      <c r="B911" s="3" t="n"/>
+    </row>
+    <row r="912">
+      <c r="B912" s="3" t="n"/>
+    </row>
+    <row r="913">
+      <c r="B913" s="3" t="n"/>
+    </row>
+    <row r="914">
+      <c r="B914" s="3" t="n"/>
+    </row>
+    <row r="915">
+      <c r="B915" s="3" t="n"/>
+    </row>
+    <row r="916">
+      <c r="B916" s="3" t="n"/>
+    </row>
+    <row r="917">
+      <c r="B917" s="3" t="n"/>
+    </row>
+    <row r="918">
+      <c r="B918" s="3" t="n"/>
+    </row>
+    <row r="919">
+      <c r="B919" s="3" t="n"/>
+    </row>
+    <row r="920">
+      <c r="B920" s="3" t="n"/>
+    </row>
+    <row r="921">
+      <c r="B921" s="3" t="n"/>
+    </row>
+    <row r="922">
+      <c r="B922" s="3" t="n"/>
+    </row>
+    <row r="923">
+      <c r="B923" s="3" t="n"/>
+    </row>
+    <row r="924">
+      <c r="B924" s="3" t="n"/>
+    </row>
+    <row r="925">
+      <c r="B925" s="3" t="n"/>
+    </row>
+    <row r="926">
+      <c r="B926" s="3" t="n"/>
+    </row>
+    <row r="927">
+      <c r="B927" s="3" t="n"/>
+    </row>
+    <row r="928">
+      <c r="B928" s="3" t="n"/>
+    </row>
+    <row r="929">
+      <c r="B929" s="3" t="n"/>
+    </row>
+    <row r="930">
+      <c r="B930" s="3" t="n"/>
+    </row>
+    <row r="931">
+      <c r="B931" s="3" t="n"/>
+    </row>
+    <row r="932">
+      <c r="B932" s="3" t="n"/>
+    </row>
+    <row r="933">
+      <c r="B933" s="3" t="n"/>
+    </row>
+    <row r="934">
+      <c r="B934" s="3" t="n"/>
+    </row>
+    <row r="935">
+      <c r="B935" s="3" t="n"/>
+    </row>
+    <row r="936">
+      <c r="B936" s="3" t="n"/>
+    </row>
+    <row r="937">
+      <c r="B937" s="3" t="n"/>
+    </row>
+    <row r="938">
+      <c r="B938" s="3" t="n"/>
+    </row>
+    <row r="939">
+      <c r="B939" s="3" t="n"/>
+    </row>
+    <row r="940">
+      <c r="B940" s="3" t="n"/>
+    </row>
+    <row r="941">
+      <c r="B941" s="3" t="n"/>
+    </row>
+    <row r="942">
+      <c r="B942" s="3" t="n"/>
+    </row>
+    <row r="943">
+      <c r="B943" s="3" t="n"/>
+    </row>
+    <row r="944">
+      <c r="B944" s="3" t="n"/>
+    </row>
+    <row r="945">
+      <c r="B945" s="3" t="n"/>
+    </row>
+    <row r="946">
+      <c r="B946" s="3" t="n"/>
+    </row>
+    <row r="947">
+      <c r="B947" s="3" t="n"/>
+    </row>
+    <row r="948">
+      <c r="B948" s="3" t="n"/>
+    </row>
+    <row r="949">
+      <c r="B949" s="3" t="n"/>
+    </row>
+    <row r="950">
+      <c r="B950" s="3" t="n"/>
+    </row>
+    <row r="951">
+      <c r="B951" s="3" t="n"/>
+    </row>
+    <row r="952">
+      <c r="B952" s="3" t="n"/>
+    </row>
+    <row r="953">
+      <c r="B953" s="3" t="n"/>
+    </row>
+    <row r="954">
+      <c r="B954" s="3" t="n"/>
+    </row>
+    <row r="955">
+      <c r="B955" s="3" t="n"/>
+    </row>
+    <row r="956">
+      <c r="B956" s="3" t="n"/>
+    </row>
+    <row r="957">
+      <c r="B957" s="3" t="n"/>
+    </row>
+    <row r="958">
+      <c r="B958" s="3" t="n"/>
+    </row>
+    <row r="959">
+      <c r="B959" s="3" t="n"/>
+    </row>
+    <row r="960">
+      <c r="B960" s="3" t="n"/>
+    </row>
+    <row r="961">
+      <c r="B961" s="3" t="n"/>
+    </row>
+    <row r="962">
+      <c r="B962" s="3" t="n"/>
+    </row>
+    <row r="963">
+      <c r="B963" s="3" t="n"/>
+    </row>
+    <row r="964">
+      <c r="B964" s="3" t="n"/>
+    </row>
+    <row r="965">
+      <c r="B965" s="3" t="n"/>
+    </row>
+    <row r="966">
+      <c r="B966" s="3" t="n"/>
+    </row>
+    <row r="967">
+      <c r="B967" s="3" t="n"/>
+    </row>
+    <row r="968">
+      <c r="B968" s="3" t="n"/>
+    </row>
+    <row r="969">
+      <c r="B969" s="3" t="n"/>
+    </row>
+    <row r="970">
+      <c r="B970" s="3" t="n"/>
+    </row>
+    <row r="971">
+      <c r="B971" s="3" t="n"/>
+    </row>
+    <row r="972">
+      <c r="B972" s="3" t="n"/>
+    </row>
+    <row r="973">
+      <c r="B973" s="3" t="n"/>
+    </row>
+    <row r="974">
+      <c r="B974" s="3" t="n"/>
+    </row>
+    <row r="975">
+      <c r="B975" s="3" t="n"/>
+    </row>
+    <row r="976">
+      <c r="B976" s="3" t="n"/>
+    </row>
+    <row r="977">
+      <c r="B977" s="3" t="n"/>
+    </row>
+    <row r="978">
+      <c r="B978" s="3" t="n"/>
+    </row>
+    <row r="979">
+      <c r="B979" s="3" t="n"/>
+    </row>
+    <row r="980">
+      <c r="B980" s="3" t="n"/>
+    </row>
+    <row r="981">
+      <c r="B981" s="3" t="n"/>
+    </row>
+    <row r="982">
+      <c r="B982" s="3" t="n"/>
+    </row>
+    <row r="983">
+      <c r="B983" s="3" t="n"/>
+    </row>
+    <row r="984">
+      <c r="B984" s="3" t="n"/>
+    </row>
+    <row r="985">
+      <c r="B985" s="3" t="n"/>
+    </row>
+    <row r="986">
+      <c r="B986" s="3" t="n"/>
+    </row>
+    <row r="987">
+      <c r="B987" s="3" t="n"/>
+    </row>
+    <row r="988">
+      <c r="B988" s="3" t="n"/>
+    </row>
+    <row r="989">
+      <c r="B989" s="3" t="n"/>
+    </row>
+    <row r="990">
+      <c r="B990" s="3" t="n"/>
+    </row>
+    <row r="991">
+      <c r="B991" s="3" t="n"/>
+    </row>
+    <row r="992">
+      <c r="B992" s="3" t="n"/>
+    </row>
+    <row r="993">
+      <c r="B993" s="3" t="n"/>
+    </row>
+    <row r="994">
+      <c r="B994" s="3" t="n"/>
+    </row>
+    <row r="995">
+      <c r="B995" s="3" t="n"/>
+    </row>
+    <row r="996">
+      <c r="B996" s="3" t="n"/>
+    </row>
+    <row r="997">
+      <c r="B997" s="3" t="n"/>
+    </row>
+    <row r="998">
+      <c r="B998" s="3" t="n"/>
+    </row>
+    <row r="999">
+      <c r="B999" s="3" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="B1000" s="3" t="n"/>
+    </row>
+    <row r="1001">
+      <c r="B1001" s="3" t="n"/>
+    </row>
+    <row r="1002">
+      <c r="B1002" s="3" t="n"/>
+    </row>
+    <row r="1003">
+      <c r="B1003" s="3" t="n"/>
+    </row>
+    <row r="1004">
+      <c r="B1004" s="3" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="B1005" s="3" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="B1006" s="3" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="B1007" s="3" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="B1008" s="3" t="n"/>
+    </row>
+    <row r="1009">
+      <c r="B1009" s="3" t="n"/>
+    </row>
+    <row r="1010">
+      <c r="B1010" s="3" t="n"/>
+    </row>
+    <row r="1011">
+      <c r="B1011" s="3" t="n"/>
+    </row>
+    <row r="1012">
+      <c r="B1012" s="3" t="n"/>
+    </row>
+    <row r="1013">
+      <c r="B1013" s="3" t="n"/>
+    </row>
+    <row r="1014">
+      <c r="B1014" s="3" t="n"/>
+    </row>
+    <row r="1015">
+      <c r="B1015" s="3" t="n"/>
+    </row>
+    <row r="1016">
+      <c r="B1016" s="3" t="n"/>
+    </row>
+    <row r="1017">
+      <c r="B1017" s="3" t="n"/>
+    </row>
+    <row r="1018">
+      <c r="B1018" s="3" t="n"/>
+    </row>
+    <row r="1019">
+      <c r="B1019" s="3" t="n"/>
+    </row>
+    <row r="1020">
+      <c r="B1020" s="3" t="n"/>
+    </row>
+    <row r="1021">
+      <c r="B1021" s="3" t="n"/>
+    </row>
+    <row r="1022">
+      <c r="B1022" s="3" t="n"/>
+    </row>
+    <row r="1023">
+      <c r="B1023" s="3" t="n"/>
+    </row>
+    <row r="1024">
+      <c r="B1024" s="3" t="n"/>
+    </row>
+    <row r="1025">
+      <c r="B1025" s="3" t="n"/>
+    </row>
+    <row r="1026">
+      <c r="B1026" s="3" t="n"/>
+    </row>
+    <row r="1027">
+      <c r="B1027" s="3" t="n"/>
+    </row>
+    <row r="1028">
+      <c r="B1028" s="3" t="n"/>
+    </row>
+    <row r="1029">
+      <c r="B1029" s="3" t="n"/>
+    </row>
+    <row r="1030">
+      <c r="B1030" s="3" t="n"/>
+    </row>
+    <row r="1031">
+      <c r="B1031" s="3" t="n"/>
+    </row>
+    <row r="1032">
+      <c r="B1032" s="3" t="n"/>
+    </row>
+    <row r="1033">
+      <c r="B1033" s="3" t="n"/>
+    </row>
+    <row r="1034">
+      <c r="B1034" s="3" t="n"/>
+    </row>
+    <row r="1035">
+      <c r="B1035" s="3" t="n"/>
+    </row>
+    <row r="1036">
+      <c r="B1036" s="3" t="n"/>
+    </row>
+    <row r="1037">
+      <c r="B1037" s="3" t="n"/>
+    </row>
+    <row r="1038">
+      <c r="B1038" s="3" t="n"/>
+    </row>
+    <row r="1039">
+      <c r="B1039" s="3" t="n"/>
+    </row>
+    <row r="1040">
+      <c r="B1040" s="3" t="n"/>
+    </row>
+    <row r="1041">
+      <c r="B1041" s="3" t="n"/>
+    </row>
+    <row r="1042">
+      <c r="B1042" s="3" t="n"/>
+    </row>
+    <row r="1043">
+      <c r="B1043" s="3" t="n"/>
+    </row>
+    <row r="1044">
+      <c r="B1044" s="3" t="n"/>
+    </row>
+    <row r="1045">
+      <c r="B1045" s="3" t="n"/>
+    </row>
+    <row r="1046">
+      <c r="B1046" s="3" t="n"/>
+    </row>
+    <row r="1047">
+      <c r="B1047" s="3" t="n"/>
+    </row>
+    <row r="1048">
+      <c r="B1048" s="3" t="n"/>
+    </row>
+    <row r="1049">
+      <c r="B1049" s="3" t="n"/>
+    </row>
+    <row r="1050">
+      <c r="B1050" s="3" t="n"/>
+    </row>
+    <row r="1051">
+      <c r="B1051" s="3" t="n"/>
+    </row>
+    <row r="1052">
+      <c r="B1052" s="3" t="n"/>
+    </row>
+    <row r="1053">
+      <c r="B1053" s="3" t="n"/>
+    </row>
+    <row r="1054">
+      <c r="B1054" s="3" t="n"/>
+    </row>
+    <row r="1055">
+      <c r="B1055" s="3" t="n"/>
+    </row>
+    <row r="1056">
+      <c r="B1056" s="3" t="n"/>
+    </row>
+    <row r="1057">
+      <c r="B1057" s="3" t="n"/>
+    </row>
+    <row r="1058">
+      <c r="B1058" s="3" t="n"/>
+    </row>
+    <row r="1059">
+      <c r="B1059" s="3" t="n"/>
+    </row>
+    <row r="1060">
+      <c r="B1060" s="3" t="n"/>
+    </row>
+    <row r="1061">
+      <c r="B1061" s="3" t="n"/>
+    </row>
+    <row r="1062">
+      <c r="B1062" s="3" t="n"/>
+    </row>
+    <row r="1063">
+      <c r="B1063" s="3" t="n"/>
+    </row>
+    <row r="1064">
+      <c r="B1064" s="3" t="n"/>
+    </row>
+    <row r="1065">
+      <c r="B1065" s="3" t="n"/>
+    </row>
+    <row r="1066">
+      <c r="B1066" s="3" t="n"/>
+    </row>
+    <row r="1067">
+      <c r="B1067" s="3" t="n"/>
+    </row>
+    <row r="1068">
+      <c r="B1068" s="3" t="n"/>
+    </row>
+    <row r="1069">
+      <c r="B1069" s="3" t="n"/>
+    </row>
+    <row r="1070">
+      <c r="B1070" s="3" t="n"/>
+    </row>
+    <row r="1071">
+      <c r="B1071" s="3" t="n"/>
+    </row>
+    <row r="1072">
+      <c r="B1072" s="3" t="n"/>
+    </row>
+    <row r="1073">
+      <c r="B1073" s="3" t="n"/>
+    </row>
+    <row r="1074">
+      <c r="B1074" s="3" t="n"/>
+    </row>
+    <row r="1075">
+      <c r="B1075" s="3" t="n"/>
+    </row>
+    <row r="1076">
+      <c r="B1076" s="3" t="n"/>
+    </row>
+    <row r="1077">
+      <c r="B1077" s="3" t="n"/>
+    </row>
+    <row r="1078">
+      <c r="B1078" s="3" t="n"/>
+    </row>
+    <row r="1079">
+      <c r="B1079" s="3" t="n"/>
+    </row>
+    <row r="1080">
+      <c r="B1080" s="3" t="n"/>
+    </row>
+    <row r="1081">
+      <c r="B1081" s="3" t="n"/>
+    </row>
+    <row r="1082">
+      <c r="B1082" s="3" t="n"/>
+    </row>
+    <row r="1083">
+      <c r="B1083" s="3" t="n"/>
+    </row>
+    <row r="1084">
+      <c r="B1084" s="3" t="n"/>
+    </row>
+    <row r="1085">
+      <c r="B1085" s="3" t="n"/>
+    </row>
+    <row r="1086">
+      <c r="B1086" s="3" t="n"/>
+    </row>
+    <row r="1087">
+      <c r="B1087" s="3" t="n"/>
+    </row>
+    <row r="1088">
+      <c r="B1088" s="3" t="n"/>
+    </row>
+    <row r="1089">
+      <c r="B1089" s="3" t="n"/>
+    </row>
+    <row r="1090">
+      <c r="B1090" s="3" t="n"/>
+    </row>
+    <row r="1091">
+      <c r="B1091" s="3" t="n"/>
+    </row>
+    <row r="1092">
+      <c r="B1092" s="3" t="n"/>
+    </row>
+    <row r="1093">
+      <c r="B1093" s="3" t="n"/>
+    </row>
+    <row r="1094">
+      <c r="B1094" s="3" t="n"/>
+    </row>
+    <row r="1095">
+      <c r="B1095" s="3" t="n"/>
+    </row>
+    <row r="1096">
+      <c r="B1096" s="3" t="n"/>
+    </row>
+    <row r="1097">
+      <c r="B1097" s="3" t="n"/>
+    </row>
+    <row r="1098">
+      <c r="B1098" s="3" t="n"/>
+    </row>
+    <row r="1099">
+      <c r="B1099" s="3" t="n"/>
+    </row>
+    <row r="1100">
+      <c r="B1100" s="3" t="n"/>
+    </row>
+    <row r="1101">
+      <c r="B1101" s="3" t="n"/>
+    </row>
+    <row r="1102">
+      <c r="B1102" s="3" t="n"/>
+    </row>
+    <row r="1103">
+      <c r="B1103" s="3" t="n"/>
+    </row>
+    <row r="1104">
+      <c r="B1104" s="3" t="n"/>
+    </row>
+    <row r="1105">
+      <c r="B1105" s="3" t="n"/>
+    </row>
+    <row r="1106">
+      <c r="B1106" s="3" t="n"/>
+    </row>
+    <row r="1107">
+      <c r="B1107" s="3" t="n"/>
+    </row>
+    <row r="1108">
+      <c r="B1108" s="3" t="n"/>
+    </row>
+    <row r="1109">
+      <c r="B1109" s="3" t="n"/>
+    </row>
+    <row r="1110">
+      <c r="B1110" s="3" t="n"/>
+    </row>
+    <row r="1111">
+      <c r="B1111" s="3" t="n"/>
+    </row>
+    <row r="1112">
+      <c r="B1112" s="3" t="n"/>
+    </row>
+    <row r="1113">
+      <c r="B1113" s="3" t="n"/>
+    </row>
+    <row r="1114">
+      <c r="B1114" s="3" t="n"/>
+    </row>
+    <row r="1115">
+      <c r="B1115" s="3" t="n"/>
+    </row>
+    <row r="1116">
+      <c r="B1116" s="3" t="n"/>
+    </row>
+    <row r="1117">
+      <c r="B1117" s="3" t="n"/>
+    </row>
+    <row r="1118">
+      <c r="B1118" s="3" t="n"/>
+    </row>
+    <row r="1119">
+      <c r="B1119" s="3" t="n"/>
+    </row>
+    <row r="1120">
+      <c r="B1120" s="3" t="n"/>
+    </row>
+    <row r="1121">
+      <c r="B1121" s="3" t="n"/>
+    </row>
+    <row r="1122">
+      <c r="B1122" s="3" t="n"/>
+    </row>
+    <row r="1123">
+      <c r="B1123" s="3" t="n"/>
+    </row>
+    <row r="1124">
+      <c r="B1124" s="3" t="n"/>
+    </row>
+    <row r="1125">
+      <c r="B1125" s="3" t="n"/>
+    </row>
+    <row r="1126">
+      <c r="B1126" s="3" t="n"/>
+    </row>
+    <row r="1127">
+      <c r="B1127" s="3" t="n"/>
+    </row>
+    <row r="1128">
+      <c r="B1128" s="3" t="n"/>
+    </row>
+    <row r="1129">
+      <c r="B1129" s="3" t="n"/>
+    </row>
+    <row r="1130">
+      <c r="B1130" s="3" t="n"/>
+    </row>
+    <row r="1131">
+      <c r="B1131" s="3" t="n"/>
+    </row>
+    <row r="1132">
+      <c r="B1132" s="3" t="n"/>
+    </row>
+    <row r="1133">
+      <c r="B1133" s="3" t="n"/>
+    </row>
+    <row r="1134">
+      <c r="B1134" s="3" t="n"/>
+    </row>
+    <row r="1135">
+      <c r="B1135" s="3" t="n"/>
+    </row>
+    <row r="1136">
+      <c r="B1136" s="3" t="n"/>
+    </row>
+    <row r="1137">
+      <c r="B1137" s="3" t="n"/>
+    </row>
+    <row r="1138">
+      <c r="B1138" s="3" t="n"/>
+    </row>
+    <row r="1139">
+      <c r="B1139" s="3" t="n"/>
+    </row>
+    <row r="1140">
+      <c r="B1140" s="3" t="n"/>
+    </row>
+    <row r="1141">
+      <c r="B1141" s="3" t="n"/>
+    </row>
+    <row r="1142">
+      <c r="B1142" s="3" t="n"/>
+    </row>
+    <row r="1143">
+      <c r="B1143" s="3" t="n"/>
+    </row>
+    <row r="1144">
+      <c r="B1144" s="3" t="n"/>
+    </row>
+    <row r="1145">
+      <c r="B1145" s="3" t="n"/>
+    </row>
+    <row r="1146">
+      <c r="B1146" s="3" t="n"/>
+    </row>
+    <row r="1147">
+      <c r="B1147" s="3" t="n"/>
+    </row>
+    <row r="1148">
+      <c r="B1148" s="3" t="n"/>
+    </row>
+    <row r="1149">
+      <c r="B1149" s="3" t="n"/>
+    </row>
+    <row r="1150">
+      <c r="B1150" s="3" t="n"/>
+    </row>
+    <row r="1151">
+      <c r="B1151" s="3" t="n"/>
+    </row>
+    <row r="1152">
+      <c r="B1152" s="3" t="n"/>
+    </row>
+    <row r="1153">
+      <c r="B1153" s="3" t="n"/>
+    </row>
+    <row r="1154">
+      <c r="B1154" s="3" t="n"/>
+    </row>
+    <row r="1155">
+      <c r="B1155" s="3" t="n"/>
+    </row>
+    <row r="1156">
+      <c r="B1156" s="3" t="n"/>
+    </row>
+    <row r="1157">
+      <c r="B1157" s="3" t="n"/>
+    </row>
+    <row r="1158">
+      <c r="B1158" s="3" t="n"/>
+    </row>
+    <row r="1159">
+      <c r="B1159" s="3" t="n"/>
+    </row>
+    <row r="1160">
+      <c r="B1160" s="3" t="n"/>
+    </row>
+    <row r="1161">
+      <c r="B1161" s="3" t="n"/>
+    </row>
+    <row r="1162">
+      <c r="B1162" s="3" t="n"/>
+    </row>
+    <row r="1163">
+      <c r="B1163" s="3" t="n"/>
+    </row>
+    <row r="1164">
+      <c r="B1164" s="3" t="n"/>
+    </row>
+    <row r="1165">
+      <c r="B1165" s="3" t="n"/>
+    </row>
+    <row r="1166">
+      <c r="B1166" s="3" t="n"/>
+    </row>
+    <row r="1167">
+      <c r="B1167" s="3" t="n"/>
+    </row>
+    <row r="1168">
+      <c r="B1168" s="3" t="n"/>
+    </row>
+    <row r="1169">
+      <c r="B1169" s="3" t="n"/>
+    </row>
+    <row r="1170">
+      <c r="B1170" s="3" t="n"/>
+    </row>
+    <row r="1171">
+      <c r="B1171" s="3" t="n"/>
+    </row>
+    <row r="1172">
+      <c r="B1172" s="3" t="n"/>
+    </row>
+    <row r="1173">
+      <c r="B1173" s="3" t="n"/>
+    </row>
+    <row r="1174">
+      <c r="B1174" s="3" t="n"/>
+    </row>
+    <row r="1175">
+      <c r="B1175" s="3" t="n"/>
+    </row>
+    <row r="1176">
+      <c r="B1176" s="3" t="n"/>
+    </row>
+    <row r="1177">
+      <c r="B1177" s="3" t="n"/>
+    </row>
+    <row r="1178">
+      <c r="B1178" s="3" t="n"/>
+    </row>
+    <row r="1179">
+      <c r="B1179" s="3" t="n"/>
+    </row>
+    <row r="1180">
+      <c r="B1180" s="3" t="n"/>
+    </row>
+    <row r="1181">
+      <c r="B1181" s="3" t="n"/>
+    </row>
+    <row r="1182">
+      <c r="B1182" s="3" t="n"/>
+    </row>
+    <row r="1183">
+      <c r="B1183" s="3" t="n"/>
+    </row>
+    <row r="1184">
+      <c r="B1184" s="3" t="n"/>
+    </row>
+    <row r="1185">
+      <c r="B1185" s="3" t="n"/>
+    </row>
+    <row r="1186">
+      <c r="B1186" s="3" t="n"/>
+    </row>
+    <row r="1187">
+      <c r="B1187" s="3" t="n"/>
+    </row>
+    <row r="1188">
+      <c r="B1188" s="3" t="n"/>
+    </row>
+    <row r="1189">
+      <c r="B1189" s="3" t="n"/>
+    </row>
+    <row r="1190">
+      <c r="B1190" s="3" t="n"/>
+    </row>
+    <row r="1191">
+      <c r="B1191" s="3" t="n"/>
+    </row>
+    <row r="1192">
+      <c r="B1192" s="3" t="n"/>
+    </row>
+    <row r="1193">
+      <c r="B1193" s="3" t="n"/>
+    </row>
+    <row r="1194">
+      <c r="B1194" s="3" t="n"/>
+    </row>
+    <row r="1195">
+      <c r="B1195" s="3" t="n"/>
+    </row>
+    <row r="1196">
+      <c r="B1196" s="3" t="n"/>
+    </row>
+    <row r="1197">
+      <c r="B1197" s="3" t="n"/>
+    </row>
+    <row r="1198">
+      <c r="B1198" s="3" t="n"/>
+    </row>
+    <row r="1199">
+      <c r="B1199" s="3" t="n"/>
+    </row>
+    <row r="1200">
+      <c r="B1200" s="3" t="n"/>
+    </row>
+    <row r="1201">
+      <c r="B1201" s="3" t="n"/>
+    </row>
+    <row r="1202">
+      <c r="B1202" s="3" t="n"/>
+    </row>
+    <row r="1203">
+      <c r="B1203" s="3" t="n"/>
+    </row>
+    <row r="1204">
+      <c r="B1204" s="3" t="n"/>
+    </row>
+    <row r="1205">
+      <c r="B1205" s="3" t="n"/>
+    </row>
+    <row r="1206">
+      <c r="B1206" s="3" t="n"/>
+    </row>
+    <row r="1207">
+      <c r="B1207" s="3" t="n"/>
+    </row>
+    <row r="1208">
+      <c r="B1208" s="3" t="n"/>
+    </row>
+    <row r="1209">
+      <c r="B1209" s="3" t="n"/>
+    </row>
+    <row r="1210">
+      <c r="B1210" s="3" t="n"/>
+    </row>
+    <row r="1211">
+      <c r="B1211" s="3" t="n"/>
+    </row>
+    <row r="1212">
+      <c r="B1212" s="3" t="n"/>
+    </row>
+    <row r="1213">
+      <c r="B1213" s="3" t="n"/>
+    </row>
+    <row r="1214">
+      <c r="B1214" s="3" t="n"/>
+    </row>
+    <row r="1215">
+      <c r="B1215" s="3" t="n"/>
+    </row>
+    <row r="1216">
+      <c r="B1216" s="3" t="n"/>
+    </row>
+    <row r="1217">
+      <c r="B1217" s="3" t="n"/>
+    </row>
+    <row r="1218">
+      <c r="B1218" s="3" t="n"/>
+    </row>
+    <row r="1219">
+      <c r="B1219" s="3" t="n"/>
+    </row>
+    <row r="1220">
+      <c r="B1220" s="3" t="n"/>
+    </row>
+    <row r="1221">
+      <c r="B1221" s="3" t="n"/>
+    </row>
+    <row r="1222">
+      <c r="B1222" s="3" t="n"/>
+    </row>
+    <row r="1223">
+      <c r="B1223" s="3" t="n"/>
+    </row>
+    <row r="1224">
+      <c r="B1224" s="3" t="n"/>
+    </row>
+    <row r="1225">
+      <c r="B1225" s="3" t="n"/>
+    </row>
+    <row r="1226">
+      <c r="B1226" s="3" t="n"/>
+    </row>
+    <row r="1227">
+      <c r="B1227" s="3" t="n"/>
+    </row>
+    <row r="1228">
+      <c r="B1228" s="3" t="n"/>
+    </row>
+    <row r="1229">
+      <c r="B1229" s="3" t="n"/>
+    </row>
+    <row r="1230">
+      <c r="B1230" s="3" t="n"/>
+    </row>
+    <row r="1231">
+      <c r="B1231" s="3" t="n"/>
+    </row>
+    <row r="1232">
+      <c r="B1232" s="3" t="n"/>
+    </row>
+    <row r="1233">
+      <c r="B1233" s="3" t="n"/>
+    </row>
+    <row r="1234">
+      <c r="B1234" s="3" t="n"/>
+    </row>
+    <row r="1235">
+      <c r="B1235" s="3" t="n"/>
+    </row>
+    <row r="1236">
+      <c r="B1236" s="3" t="n"/>
+    </row>
+    <row r="1237">
+      <c r="B1237" s="3" t="n"/>
+    </row>
+    <row r="1238">
+      <c r="B1238" s="3" t="n"/>
+    </row>
+    <row r="1239">
+      <c r="B1239" s="3" t="n"/>
+    </row>
+    <row r="1240">
+      <c r="B1240" s="3" t="n"/>
+    </row>
+    <row r="1241">
+      <c r="B1241" s="3" t="n"/>
+    </row>
+    <row r="1242">
+      <c r="B1242" s="3" t="n"/>
+    </row>
+    <row r="1243">
+      <c r="B1243" s="3" t="n"/>
+    </row>
+    <row r="1244">
+      <c r="B1244" s="3" t="n"/>
+    </row>
+    <row r="1245">
+      <c r="B1245" s="3" t="n"/>
+    </row>
+    <row r="1246">
+      <c r="B1246" s="3" t="n"/>
+    </row>
+    <row r="1247">
+      <c r="B1247" s="3" t="n"/>
+    </row>
+    <row r="1248">
+      <c r="B1248" s="3" t="n"/>
+    </row>
+    <row r="1249">
+      <c r="B1249" s="3" t="n"/>
+    </row>
+    <row r="1250">
+      <c r="B1250" s="3" t="n"/>
+    </row>
+    <row r="1251">
+      <c r="B1251" s="3" t="n"/>
+    </row>
+    <row r="1252">
+      <c r="B1252" s="3" t="n"/>
+    </row>
+    <row r="1253">
+      <c r="B1253" s="3" t="n"/>
+    </row>
+    <row r="1254">
+      <c r="B1254" s="3" t="n"/>
+    </row>
+    <row r="1255">
+      <c r="B1255" s="3" t="n"/>
+    </row>
+    <row r="1256">
+      <c r="B1256" s="3" t="n"/>
+    </row>
+    <row r="1257">
+      <c r="B1257" s="3" t="n"/>
+    </row>
+    <row r="1258">
+      <c r="B1258" s="3" t="n"/>
+    </row>
+    <row r="1259">
+      <c r="B1259" s="3" t="n"/>
+    </row>
+    <row r="1260">
+      <c r="B1260" s="3" t="n"/>
+    </row>
+    <row r="1261">
+      <c r="B1261" s="3" t="n"/>
+    </row>
+    <row r="1262">
+      <c r="B1262" s="3" t="n"/>
+    </row>
+    <row r="1263">
+      <c r="B1263" s="3" t="n"/>
+    </row>
+    <row r="1264">
+      <c r="B1264" s="3" t="n"/>
+    </row>
+    <row r="1265">
+      <c r="B1265" s="3" t="n"/>
+    </row>
+    <row r="1266">
+      <c r="B1266" s="3" t="n"/>
+    </row>
+    <row r="1267">
+      <c r="B1267" s="3" t="n"/>
+    </row>
+    <row r="1268">
+      <c r="B1268" s="3" t="n"/>
+    </row>
+    <row r="1269">
+      <c r="B1269" s="3" t="n"/>
+    </row>
+    <row r="1270">
+      <c r="B1270" s="3" t="n"/>
+    </row>
+    <row r="1271">
+      <c r="B1271" s="3" t="n"/>
+    </row>
+    <row r="1272">
+      <c r="B1272" s="3" t="n"/>
+    </row>
+    <row r="1273">
+      <c r="B1273" s="3" t="n"/>
+    </row>
+    <row r="1274">
+      <c r="B1274" s="3" t="n"/>
+    </row>
+    <row r="1275">
+      <c r="B1275" s="3" t="n"/>
+    </row>
+    <row r="1276">
+      <c r="B1276" s="3" t="n"/>
+    </row>
+    <row r="1277">
+      <c r="B1277" s="3" t="n"/>
+    </row>
+    <row r="1278">
+      <c r="B1278" s="3" t="n"/>
+    </row>
+    <row r="1279">
+      <c r="B1279" s="3" t="n"/>
+    </row>
+    <row r="1280">
+      <c r="B1280" s="3" t="n"/>
+    </row>
+    <row r="1281">
+      <c r="B1281" s="3" t="n"/>
+    </row>
+    <row r="1282">
+      <c r="B1282" s="3" t="n"/>
+    </row>
+    <row r="1283">
+      <c r="B1283" s="3" t="n"/>
+    </row>
+    <row r="1284">
+      <c r="B1284" s="3" t="n"/>
+    </row>
+    <row r="1285">
+      <c r="B1285" s="3" t="n"/>
+    </row>
+    <row r="1286">
+      <c r="B1286" s="3" t="n"/>
+    </row>
+    <row r="1287">
+      <c r="B1287" s="3" t="n"/>
+    </row>
+    <row r="1288">
+      <c r="B1288" s="3" t="n"/>
+    </row>
+    <row r="1289">
+      <c r="B1289" s="3" t="n"/>
+    </row>
+    <row r="1290">
+      <c r="B1290" s="3" t="n"/>
+    </row>
+    <row r="1291">
+      <c r="B1291" s="3" t="n"/>
+    </row>
+    <row r="1292">
+      <c r="B1292" s="3" t="n"/>
+    </row>
+    <row r="1293">
+      <c r="B1293" s="3" t="n"/>
+    </row>
+    <row r="1294">
+      <c r="B1294" s="3" t="n"/>
+    </row>
+    <row r="1295">
+      <c r="B1295" s="3" t="n"/>
+    </row>
+    <row r="1296">
+      <c r="B1296" s="3" t="n"/>
+    </row>
+    <row r="1297">
+      <c r="B1297" s="3" t="n"/>
+    </row>
+    <row r="1298">
+      <c r="B1298" s="3" t="n"/>
+    </row>
+    <row r="1299">
+      <c r="B1299" s="3" t="n"/>
+    </row>
+    <row r="1300">
+      <c r="B1300" s="3" t="n"/>
+    </row>
+    <row r="1301">
+      <c r="B1301" s="3" t="n"/>
+    </row>
+    <row r="1302">
+      <c r="B1302" s="3" t="n"/>
+    </row>
+    <row r="1303">
+      <c r="B1303" s="3" t="n"/>
+    </row>
+    <row r="1304">
+      <c r="B1304" s="3" t="n"/>
+    </row>
+    <row r="1305">
+      <c r="B1305" s="3" t="n"/>
+    </row>
+    <row r="1306">
+      <c r="B1306" s="3" t="n"/>
+    </row>
+    <row r="1307">
+      <c r="B1307" s="3" t="n"/>
+    </row>
+    <row r="1308">
+      <c r="B1308" s="3" t="n"/>
+    </row>
+    <row r="1309">
+      <c r="B1309" s="3" t="n"/>
+    </row>
+    <row r="1310">
+      <c r="B1310" s="3" t="n"/>
+    </row>
+    <row r="1311">
+      <c r="B1311" s="3" t="n"/>
+    </row>
+    <row r="1312">
+      <c r="B1312" s="3" t="n"/>
+    </row>
+    <row r="1313">
+      <c r="B1313" s="3" t="n"/>
+    </row>
+    <row r="1314">
+      <c r="B1314" s="3" t="n"/>
+    </row>
+    <row r="1315">
+      <c r="B1315" s="3" t="n"/>
+    </row>
+    <row r="1316">
+      <c r="B1316" s="3" t="n"/>
+    </row>
+    <row r="1317">
+      <c r="B1317" s="3" t="n"/>
+    </row>
+    <row r="1318">
+      <c r="B1318" s="3" t="n"/>
+    </row>
+    <row r="1319">
+      <c r="B1319" s="3" t="n"/>
+    </row>
+    <row r="1320">
+      <c r="B1320" s="3" t="n"/>
+    </row>
+    <row r="1321">
+      <c r="B1321" s="3" t="n"/>
+    </row>
+    <row r="1322">
+      <c r="B1322" s="3" t="n"/>
+    </row>
+    <row r="1323">
+      <c r="B1323" s="3" t="n"/>
+    </row>
+    <row r="1324">
+      <c r="B1324" s="3" t="n"/>
+    </row>
+    <row r="1325">
+      <c r="B1325" s="3" t="n"/>
+    </row>
+    <row r="1326">
+      <c r="B1326" s="3" t="n"/>
+    </row>
+    <row r="1327">
+      <c r="B1327" s="3" t="n"/>
+    </row>
+    <row r="1328">
+      <c r="B1328" s="3" t="n"/>
+    </row>
+    <row r="1329">
+      <c r="B1329" s="3" t="n"/>
+    </row>
+    <row r="1330">
+      <c r="B1330" s="3" t="n"/>
+    </row>
+    <row r="1331">
+      <c r="B1331" s="3" t="n"/>
+    </row>
+    <row r="1332">
+      <c r="B1332" s="3" t="n"/>
+    </row>
+    <row r="1333">
+      <c r="B1333" s="3" t="n"/>
+    </row>
+    <row r="1334">
+      <c r="B1334" s="3" t="n"/>
+    </row>
+    <row r="1335">
+      <c r="B1335" s="3" t="n"/>
+    </row>
+    <row r="1336">
+      <c r="B1336" s="3" t="n"/>
+    </row>
+    <row r="1337">
+      <c r="B1337" s="3" t="n"/>
+    </row>
+    <row r="1338">
+      <c r="B1338" s="3" t="n"/>
+    </row>
+    <row r="1339">
+      <c r="B1339" s="3" t="n"/>
+    </row>
+    <row r="1340">
+      <c r="B1340" s="3" t="n"/>
+    </row>
+    <row r="1341">
+      <c r="B1341" s="3" t="n"/>
+    </row>
+    <row r="1342">
+      <c r="B1342" s="3" t="n"/>
+    </row>
+    <row r="1343">
+      <c r="B1343" s="3" t="n"/>
+    </row>
+    <row r="1344">
+      <c r="B1344" s="3" t="n"/>
+    </row>
+    <row r="1345">
+      <c r="B1345" s="3" t="n"/>
+    </row>
+    <row r="1346">
+      <c r="B1346" s="3" t="n"/>
+    </row>
+    <row r="1347">
+      <c r="B1347" s="3" t="n"/>
+    </row>
+    <row r="1348">
+      <c r="B1348" s="3" t="n"/>
+    </row>
+    <row r="1349">
+      <c r="B1349" s="3" t="n"/>
+    </row>
+    <row r="1350">
+      <c r="B1350" s="3" t="n"/>
+    </row>
+    <row r="1351">
+      <c r="B1351" s="3" t="n"/>
+    </row>
+    <row r="1352">
+      <c r="B1352" s="3" t="n"/>
+    </row>
+    <row r="1353">
+      <c r="B1353" s="3" t="n"/>
+    </row>
+    <row r="1354">
+      <c r="B1354" s="3" t="n"/>
+    </row>
+    <row r="1355">
+      <c r="B1355" s="3" t="n"/>
+    </row>
+    <row r="1356">
+      <c r="B1356" s="3" t="n"/>
+    </row>
+    <row r="1357">
+      <c r="B1357" s="3" t="n"/>
+    </row>
+    <row r="1358">
+      <c r="B1358" s="3" t="n"/>
+    </row>
+    <row r="1359">
+      <c r="B1359" s="3" t="n"/>
+    </row>
+    <row r="1360">
+      <c r="B1360" s="3" t="n"/>
+    </row>
+    <row r="1361">
+      <c r="B1361" s="3" t="n"/>
+    </row>
+    <row r="1362">
+      <c r="B1362" s="3" t="n"/>
+    </row>
+    <row r="1363">
+      <c r="B1363" s="3" t="n"/>
+    </row>
+    <row r="1364">
+      <c r="B1364" s="3" t="n"/>
+    </row>
+    <row r="1365">
+      <c r="B1365" s="3" t="n"/>
+    </row>
+    <row r="1366">
+      <c r="B1366" s="3" t="n"/>
+    </row>
+    <row r="1367">
+      <c r="B1367" s="3" t="n"/>
+    </row>
+    <row r="1368">
+      <c r="B1368" s="3" t="n"/>
+    </row>
+    <row r="1369">
+      <c r="B1369" s="3" t="n"/>
+    </row>
+    <row r="1370">
+      <c r="B1370" s="3" t="n"/>
+    </row>
+    <row r="1371">
+      <c r="B1371" s="3" t="n"/>
+    </row>
+    <row r="1372">
+      <c r="B1372" s="3" t="n"/>
+    </row>
+    <row r="1373">
+      <c r="B1373" s="3" t="n"/>
+    </row>
+    <row r="1374">
+      <c r="B1374" s="3" t="n"/>
+    </row>
+    <row r="1375">
+      <c r="B1375" s="3" t="n"/>
+    </row>
+    <row r="1376">
+      <c r="B1376" s="3" t="n"/>
+    </row>
+    <row r="1377">
+      <c r="B1377" s="3" t="n"/>
+    </row>
+    <row r="1378">
+      <c r="B1378" s="3" t="n"/>
+    </row>
+    <row r="1379">
+      <c r="B1379" s="3" t="n"/>
+    </row>
+    <row r="1380">
+      <c r="B1380" s="3" t="n"/>
+    </row>
+    <row r="1381">
+      <c r="B1381" s="3" t="n"/>
+    </row>
+    <row r="1382">
+      <c r="B1382" s="3" t="n"/>
+    </row>
+    <row r="1383">
+      <c r="B1383" s="3" t="n"/>
+    </row>
+    <row r="1384">
+      <c r="B1384" s="3" t="n"/>
+    </row>
+    <row r="1385">
+      <c r="B1385" s="3" t="n"/>
+    </row>
+    <row r="1386">
+      <c r="B1386" s="3" t="n"/>
+    </row>
+    <row r="1387">
+      <c r="B1387" s="3" t="n"/>
+    </row>
+    <row r="1388">
+      <c r="B1388" s="3" t="n"/>
+    </row>
+    <row r="1389">
+      <c r="B1389" s="3" t="n"/>
+    </row>
+    <row r="1390">
+      <c r="B1390" s="3" t="n"/>
+    </row>
+    <row r="1391">
+      <c r="B1391" s="3" t="n"/>
+    </row>
+    <row r="1392">
+      <c r="B1392" s="3" t="n"/>
+    </row>
+    <row r="1393">
+      <c r="B1393" s="3" t="n"/>
+    </row>
+    <row r="1394">
+      <c r="B1394" s="3" t="n"/>
+    </row>
+    <row r="1395">
+      <c r="B1395" s="3" t="n"/>
+    </row>
+    <row r="1396">
+      <c r="B1396" s="3" t="n"/>
+    </row>
+    <row r="1397">
+      <c r="B1397" s="3" t="n"/>
+    </row>
+    <row r="1398">
+      <c r="B1398" s="3" t="n"/>
+    </row>
+    <row r="1399">
+      <c r="B1399" s="3" t="n"/>
+    </row>
+    <row r="1400">
+      <c r="B1400" s="3" t="n"/>
+    </row>
+    <row r="1401">
+      <c r="B1401" s="3" t="n"/>
+    </row>
+    <row r="1402">
+      <c r="B1402" s="3" t="n"/>
+    </row>
+    <row r="1403">
+      <c r="B1403" s="3" t="n"/>
+    </row>
+    <row r="1404">
+      <c r="B1404" s="3" t="n"/>
+    </row>
+    <row r="1405">
+      <c r="B1405" s="3" t="n"/>
+    </row>
+    <row r="1406">
+      <c r="B1406" s="3" t="n"/>
+    </row>
+    <row r="1407">
+      <c r="B1407" s="3" t="n"/>
+    </row>
+    <row r="1408">
+      <c r="B1408" s="3" t="n"/>
+    </row>
+    <row r="1409">
+      <c r="B1409" s="3" t="n"/>
+    </row>
+    <row r="1410">
+      <c r="B1410" s="3" t="n"/>
+    </row>
+    <row r="1411">
+      <c r="B1411" s="3" t="n"/>
+    </row>
+    <row r="1412">
+      <c r="B1412" s="3" t="n"/>
+    </row>
+    <row r="1413">
+      <c r="B1413" s="3" t="n"/>
+    </row>
+    <row r="1414">
+      <c r="B1414" s="3" t="n"/>
+    </row>
+    <row r="1415">
+      <c r="B1415" s="3" t="n"/>
+    </row>
+    <row r="1416">
+      <c r="B1416" s="3" t="n"/>
+    </row>
+    <row r="1417">
+      <c r="B1417" s="3" t="n"/>
+    </row>
+    <row r="1418">
+      <c r="B1418" s="3" t="n"/>
+    </row>
+    <row r="1419">
+      <c r="B1419" s="3" t="n"/>
+    </row>
+    <row r="1420">
+      <c r="B1420" s="3" t="n"/>
+    </row>
+    <row r="1421">
+      <c r="B1421" s="3" t="n"/>
+    </row>
+    <row r="1422">
+      <c r="B1422" s="3" t="n"/>
+    </row>
+    <row r="1423">
+      <c r="B1423" s="3" t="n"/>
+    </row>
+    <row r="1424">
+      <c r="B1424" s="3" t="n"/>
+    </row>
+    <row r="1425">
+      <c r="B1425" s="3" t="n"/>
+    </row>
+    <row r="1426">
+      <c r="B1426" s="3" t="n"/>
+    </row>
+    <row r="1427">
+      <c r="B1427" s="3" t="n"/>
+    </row>
+    <row r="1428">
+      <c r="B1428" s="3" t="n"/>
+    </row>
+    <row r="1429">
+      <c r="B1429" s="3" t="n"/>
+    </row>
+    <row r="1430">
+      <c r="B1430" s="3" t="n"/>
+    </row>
+    <row r="1431">
+      <c r="B1431" s="3" t="n"/>
+    </row>
+    <row r="1432">
+      <c r="B1432" s="3" t="n"/>
+    </row>
+    <row r="1433">
+      <c r="B1433" s="3" t="n"/>
+    </row>
+    <row r="1434">
+      <c r="B1434" s="3" t="n"/>
+    </row>
+    <row r="1435">
+      <c r="B1435" s="3" t="n"/>
+    </row>
+    <row r="1436">
+      <c r="B1436" s="3" t="n"/>
+    </row>
+    <row r="1437">
+      <c r="B1437" s="3" t="n"/>
+    </row>
+    <row r="1438">
+      <c r="B1438" s="3" t="n"/>
+    </row>
+    <row r="1439">
+      <c r="B1439" s="3" t="n"/>
+    </row>
+    <row r="1440">
+      <c r="B1440" s="3" t="n"/>
+    </row>
+    <row r="1441">
+      <c r="B1441" s="3" t="n"/>
+    </row>
+    <row r="1442">
+      <c r="B1442" s="3" t="n"/>
+    </row>
+    <row r="1443">
+      <c r="B1443" s="3" t="n"/>
+    </row>
+    <row r="1444">
+      <c r="B1444" s="3" t="n"/>
+    </row>
+    <row r="1445">
+      <c r="B1445" s="3" t="n"/>
+    </row>
+    <row r="1446">
+      <c r="B1446" s="3" t="n"/>
+    </row>
+    <row r="1447">
+      <c r="B1447" s="3" t="n"/>
+    </row>
+    <row r="1448">
+      <c r="B1448" s="3" t="n"/>
+    </row>
+    <row r="1449">
+      <c r="B1449" s="3" t="n"/>
+    </row>
+    <row r="1450">
+      <c r="B1450" s="3" t="n"/>
+    </row>
+    <row r="1451">
+      <c r="B1451" s="3" t="n"/>
+    </row>
+    <row r="1452">
+      <c r="B1452" s="3" t="n"/>
+    </row>
+    <row r="1453">
+      <c r="B1453" s="3" t="n"/>
+    </row>
+    <row r="1454">
+      <c r="B1454" s="3" t="n"/>
+    </row>
+    <row r="1455">
+      <c r="B1455" s="3" t="n"/>
+    </row>
+    <row r="1456">
+      <c r="B1456" s="3" t="n"/>
+    </row>
+    <row r="1457">
+      <c r="B1457" s="3" t="n"/>
+    </row>
+    <row r="1458">
+      <c r="B1458" s="3" t="n"/>
+    </row>
+    <row r="1459">
+      <c r="B1459" s="3" t="n"/>
+    </row>
+    <row r="1460">
+      <c r="B1460" s="3" t="n"/>
+    </row>
+    <row r="1461">
+      <c r="B1461" s="3" t="n"/>
+    </row>
+    <row r="1462">
+      <c r="B1462" s="3" t="n"/>
+    </row>
+    <row r="1463">
+      <c r="B1463" s="3" t="n"/>
+    </row>
+    <row r="1464">
+      <c r="B1464" s="3" t="n"/>
+    </row>
+    <row r="1465">
+      <c r="B1465" s="3" t="n"/>
+    </row>
+    <row r="1466">
+      <c r="B1466" s="3" t="n"/>
+    </row>
+    <row r="1467">
+      <c r="B1467" s="3" t="n"/>
+    </row>
+    <row r="1468">
+      <c r="B1468" s="3" t="n"/>
+    </row>
+    <row r="1469">
+      <c r="B1469" s="3" t="n"/>
+    </row>
+    <row r="1470">
+      <c r="B1470" s="3" t="n"/>
+    </row>
+    <row r="1471">
+      <c r="B1471" s="3" t="n"/>
+    </row>
+    <row r="1472">
+      <c r="B1472" s="3" t="n"/>
+    </row>
+    <row r="1473">
+      <c r="B1473" s="3" t="n"/>
+    </row>
+    <row r="1474">
+      <c r="B1474" s="3" t="n"/>
+    </row>
+    <row r="1475">
+      <c r="B1475" s="3" t="n"/>
+    </row>
+    <row r="1476">
+      <c r="B1476" s="3" t="n"/>
+    </row>
+    <row r="1477">
+      <c r="B1477" s="3" t="n"/>
+    </row>
+    <row r="1478">
+      <c r="B1478" s="3" t="n"/>
+    </row>
+    <row r="1479">
+      <c r="B1479" s="3" t="n"/>
+    </row>
+    <row r="1480">
+      <c r="B1480" s="3" t="n"/>
+    </row>
+    <row r="1481">
+      <c r="B1481" s="3" t="n"/>
+    </row>
+    <row r="1482">
+      <c r="B1482" s="3" t="n"/>
+    </row>
+    <row r="1483">
+      <c r="B1483" s="3" t="n"/>
+    </row>
+    <row r="1484">
+      <c r="B1484" s="3" t="n"/>
+    </row>
+    <row r="1485">
+      <c r="B1485" s="3" t="n"/>
+    </row>
+    <row r="1486">
+      <c r="B1486" s="3" t="n"/>
+    </row>
+    <row r="1487">
+      <c r="B1487" s="3" t="n"/>
+    </row>
+    <row r="1488">
+      <c r="B1488" s="3" t="n"/>
+    </row>
+    <row r="1489">
+      <c r="B1489" s="3" t="n"/>
+    </row>
+    <row r="1490">
+      <c r="B1490" s="3" t="n"/>
+    </row>
+    <row r="1491">
+      <c r="B1491" s="3" t="n"/>
+    </row>
+    <row r="1492">
+      <c r="B1492" s="3" t="n"/>
+    </row>
+    <row r="1493">
+      <c r="B1493" s="3" t="n"/>
+    </row>
+    <row r="1494">
+      <c r="B1494" s="3" t="n"/>
+    </row>
+    <row r="1495">
+      <c r="B1495" s="3" t="n"/>
+    </row>
+    <row r="1496">
+      <c r="B1496" s="3" t="n"/>
+    </row>
+    <row r="1497">
+      <c r="B1497" s="3" t="n"/>
+    </row>
+    <row r="1498">
+      <c r="B1498" s="3" t="n"/>
+    </row>
+    <row r="1499">
+      <c r="B1499" s="3" t="n"/>
+    </row>
+    <row r="1500">
+      <c r="B1500" s="3" t="n"/>
+    </row>
+    <row r="1501">
+      <c r="B1501" s="3" t="n"/>
+    </row>
+    <row r="1502">
+      <c r="B1502" s="3" t="n"/>
+    </row>
+    <row r="1503">
+      <c r="B1503" s="3" t="n"/>
+    </row>
+    <row r="1504">
+      <c r="B1504" s="3" t="n"/>
+    </row>
+    <row r="1505">
+      <c r="B1505" s="3" t="n"/>
+    </row>
+    <row r="1506">
+      <c r="B1506" s="3" t="n"/>
+    </row>
+    <row r="1507">
+      <c r="B1507" s="3" t="n"/>
+    </row>
+    <row r="1508">
+      <c r="B1508" s="3" t="n"/>
+    </row>
+    <row r="1509">
+      <c r="B1509" s="3" t="n"/>
+    </row>
+    <row r="1510">
+      <c r="B1510" s="3" t="n"/>
+    </row>
+    <row r="1511">
+      <c r="B1511" s="3" t="n"/>
+    </row>
+    <row r="1512">
+      <c r="B1512" s="3" t="n"/>
+    </row>
+    <row r="1513">
+      <c r="B1513" s="3" t="n"/>
+    </row>
+    <row r="1514">
+      <c r="B1514" s="3" t="n"/>
+    </row>
+    <row r="1515">
+      <c r="B1515" s="3" t="n"/>
+    </row>
+    <row r="1516">
+      <c r="B1516" s="3" t="n"/>
+    </row>
+    <row r="1517">
+      <c r="B1517" s="3" t="n"/>
+    </row>
+    <row r="1518">
+      <c r="B1518" s="3" t="n"/>
+    </row>
+    <row r="1519">
+      <c r="B1519" s="3" t="n"/>
+    </row>
+    <row r="1520">
+      <c r="B1520" s="3" t="n"/>
+    </row>
+    <row r="1521">
+      <c r="B1521" s="3" t="n"/>
+    </row>
+    <row r="1522">
+      <c r="B1522" s="3" t="n"/>
+    </row>
+    <row r="1523">
+      <c r="B1523" s="3" t="n"/>
+    </row>
+    <row r="1524">
+      <c r="B1524" s="3" t="n"/>
+    </row>
+    <row r="1525">
+      <c r="B1525" s="3" t="n"/>
+    </row>
+    <row r="1526">
+      <c r="B1526" s="3" t="n"/>
+    </row>
+    <row r="1527">
+      <c r="B1527" s="3" t="n"/>
+    </row>
+    <row r="1528">
+      <c r="B1528" s="3" t="n"/>
+    </row>
+    <row r="1529">
+      <c r="B1529" s="3" t="n"/>
+    </row>
+    <row r="1530">
+      <c r="B1530" s="3" t="n"/>
+    </row>
+    <row r="1531">
+      <c r="B1531" s="3" t="n"/>
+    </row>
+    <row r="1532">
+      <c r="B1532" s="3" t="n"/>
+    </row>
+    <row r="1533">
+      <c r="B1533" s="3" t="n"/>
+    </row>
+    <row r="1534">
+      <c r="B1534" s="3" t="n"/>
+    </row>
+    <row r="1535">
+      <c r="B1535" s="3" t="n"/>
+    </row>
+    <row r="1536">
+      <c r="B1536" s="3" t="n"/>
+    </row>
+    <row r="1537">
+      <c r="B1537" s="3" t="n"/>
+    </row>
+    <row r="1538">
+      <c r="B1538" s="3" t="n"/>
+    </row>
+    <row r="1539">
+      <c r="B1539" s="3" t="n"/>
+    </row>
+    <row r="1540">
+      <c r="B1540" s="3" t="n"/>
+    </row>
+    <row r="1541">
+      <c r="B1541" s="3" t="n"/>
+    </row>
+    <row r="1542">
+      <c r="B1542" s="3" t="n"/>
+    </row>
+    <row r="1543">
+      <c r="B1543" s="3" t="n"/>
+    </row>
+    <row r="1544">
+      <c r="B1544" s="3" t="n"/>
+    </row>
+    <row r="1545">
+      <c r="B1545" s="3" t="n"/>
+    </row>
+    <row r="1546">
+      <c r="B1546" s="3" t="n"/>
+    </row>
+    <row r="1547">
+      <c r="B1547" s="3" t="n"/>
+    </row>
+    <row r="1548">
+      <c r="B1548" s="3" t="n"/>
+    </row>
+    <row r="1549">
+      <c r="B1549" s="3" t="n"/>
+    </row>
+    <row r="1550">
+      <c r="B1550" s="3" t="n"/>
+    </row>
+    <row r="1551">
+      <c r="B1551" s="3" t="n"/>
+    </row>
+    <row r="1552">
+      <c r="B1552" s="3" t="n"/>
+    </row>
+    <row r="1553">
+      <c r="B1553" s="3" t="n"/>
+    </row>
+    <row r="1554">
+      <c r="B1554" s="3" t="n"/>
+    </row>
+    <row r="1555">
+      <c r="B1555" s="3" t="n"/>
+    </row>
+    <row r="1556">
+      <c r="B1556" s="3" t="n"/>
+    </row>
+    <row r="1557">
+      <c r="B1557" s="3" t="n"/>
+    </row>
+    <row r="1558">
+      <c r="B1558" s="3" t="n"/>
+    </row>
+    <row r="1559">
+      <c r="B1559" s="3" t="n"/>
+    </row>
+    <row r="1560">
+      <c r="B1560" s="3" t="n"/>
+    </row>
+    <row r="1561">
+      <c r="B1561" s="3" t="n"/>
+    </row>
+    <row r="1562">
+      <c r="B1562" s="3" t="n"/>
+    </row>
+    <row r="1563">
+      <c r="B1563" s="3" t="n"/>
+    </row>
+    <row r="1564">
+      <c r="B1564" s="3" t="n"/>
+    </row>
+    <row r="1565">
+      <c r="B1565" s="3" t="n"/>
+    </row>
+    <row r="1566">
+      <c r="B1566" s="3" t="n"/>
+    </row>
+    <row r="1567">
+      <c r="B1567" s="3" t="n"/>
+    </row>
+    <row r="1568">
+      <c r="B1568" s="3" t="n"/>
+    </row>
+    <row r="1569">
+      <c r="B1569" s="3" t="n"/>
+    </row>
+    <row r="1570">
+      <c r="B1570" s="3" t="n"/>
+    </row>
+    <row r="1571">
+      <c r="B1571" s="3" t="n"/>
+    </row>
+    <row r="1572">
+      <c r="B1572" s="3" t="n"/>
+    </row>
+    <row r="1573">
+      <c r="B1573" s="3" t="n"/>
+    </row>
+    <row r="1574">
+      <c r="B1574" s="3" t="n"/>
+    </row>
+    <row r="1575">
+      <c r="B1575" s="3" t="n"/>
+    </row>
+    <row r="1576">
+      <c r="B1576" s="3" t="n"/>
+    </row>
+    <row r="1577">
+      <c r="B1577" s="3" t="n"/>
+    </row>
+    <row r="1578">
+      <c r="B1578" s="3" t="n"/>
+    </row>
+    <row r="1579">
+      <c r="B1579" s="3" t="n"/>
+    </row>
+    <row r="1580">
+      <c r="B1580" s="3" t="n"/>
+    </row>
+    <row r="1581">
+      <c r="B1581" s="3" t="n"/>
+    </row>
+    <row r="1582">
+      <c r="B1582" s="3" t="n"/>
+    </row>
+    <row r="1583">
+      <c r="B1583" s="3" t="n"/>
+    </row>
+    <row r="1584">
+      <c r="B1584" s="3" t="n"/>
+    </row>
+    <row r="1585">
+      <c r="B1585" s="3" t="n"/>
+    </row>
+    <row r="1586">
+      <c r="B1586" s="3" t="n"/>
+    </row>
+    <row r="1587">
+      <c r="B1587" s="3" t="n"/>
+    </row>
+    <row r="1588">
+      <c r="B1588" s="3" t="n"/>
+    </row>
+    <row r="1589">
+      <c r="B1589" s="3" t="n"/>
+    </row>
+    <row r="1590">
+      <c r="B1590" s="3" t="n"/>
+    </row>
+    <row r="1591">
+      <c r="B1591" s="3" t="n"/>
+    </row>
+    <row r="1592">
+      <c r="B1592" s="3" t="n"/>
+    </row>
+    <row r="1593">
+      <c r="B1593" s="3" t="n"/>
+    </row>
+    <row r="1594">
+      <c r="B1594" s="3" t="n"/>
+    </row>
+    <row r="1595">
+      <c r="B1595" s="3" t="n"/>
+    </row>
+    <row r="1596">
+      <c r="B1596" s="3" t="n"/>
+    </row>
+    <row r="1597">
+      <c r="B1597" s="3" t="n"/>
+    </row>
+    <row r="1598">
+      <c r="B1598" s="3" t="n"/>
+    </row>
+    <row r="1599">
+      <c r="B1599" s="3" t="n"/>
+    </row>
+    <row r="1600">
+      <c r="B1600" s="3" t="n"/>
+    </row>
+    <row r="1601">
+      <c r="B1601" s="3" t="n"/>
+    </row>
+    <row r="1602">
+      <c r="B1602" s="3" t="n"/>
+    </row>
+    <row r="1603">
+      <c r="B1603" s="3" t="n"/>
+    </row>
+    <row r="1604">
+      <c r="B1604" s="3" t="n"/>
+    </row>
+    <row r="1605">
+      <c r="B1605" s="3" t="n"/>
+    </row>
+    <row r="1606">
+      <c r="B1606" s="3" t="n"/>
+    </row>
+    <row r="1607">
+      <c r="B1607" s="3" t="n"/>
+    </row>
+    <row r="1608">
+      <c r="B1608" s="3" t="n"/>
+    </row>
+    <row r="1609">
+      <c r="B1609" s="3" t="n"/>
+    </row>
+    <row r="1610">
+      <c r="B1610" s="3" t="n"/>
+    </row>
+    <row r="1611">
+      <c r="B1611" s="3" t="n"/>
+    </row>
+    <row r="1612">
+      <c r="B1612" s="3" t="n"/>
+    </row>
+    <row r="1613">
+      <c r="B1613" s="3" t="n"/>
+    </row>
+    <row r="1614">
+      <c r="B1614" s="3" t="n"/>
+    </row>
+    <row r="1615">
+      <c r="B1615" s="3" t="n"/>
+    </row>
+    <row r="1616">
+      <c r="B1616" s="3" t="n"/>
+    </row>
+    <row r="1617">
+      <c r="B1617" s="3" t="n"/>
+    </row>
+    <row r="1618">
+      <c r="B1618" s="3" t="n"/>
+    </row>
+    <row r="1619">
+      <c r="B1619" s="3" t="n"/>
+    </row>
+    <row r="1620">
+      <c r="B1620" s="3" t="n"/>
+    </row>
+    <row r="1621">
+      <c r="B1621" s="3" t="n"/>
+    </row>
+    <row r="1622">
+      <c r="B1622" s="3" t="n"/>
+    </row>
+    <row r="1623">
+      <c r="B1623" s="3" t="n"/>
+    </row>
+    <row r="1624">
+      <c r="B1624" s="3" t="n"/>
+    </row>
+    <row r="1625">
+      <c r="B1625" s="3" t="n"/>
+    </row>
+    <row r="1626">
+      <c r="B1626" s="3" t="n"/>
+    </row>
+    <row r="1627">
+      <c r="B1627" s="3" t="n"/>
+    </row>
+    <row r="1628">
+      <c r="B1628" s="3" t="n"/>
+    </row>
+    <row r="1629">
+      <c r="B1629" s="3" t="n"/>
+    </row>
+    <row r="1630">
+      <c r="B1630" s="3" t="n"/>
+    </row>
+    <row r="1631">
+      <c r="B1631" s="3" t="n"/>
+    </row>
+    <row r="1632">
+      <c r="B1632" s="3" t="n"/>
+    </row>
+    <row r="1633">
+      <c r="B1633" s="3" t="n"/>
+    </row>
+    <row r="1634">
+      <c r="B1634" s="3" t="n"/>
+    </row>
+    <row r="1635">
+      <c r="B1635" s="3" t="n"/>
+    </row>
+    <row r="1636">
+      <c r="B1636" s="3" t="n"/>
+    </row>
+    <row r="1637">
+      <c r="B1637" s="3" t="n"/>
+    </row>
+    <row r="1638">
+      <c r="B1638" s="3" t="n"/>
+    </row>
+    <row r="1639">
+      <c r="B1639" s="3" t="n"/>
+    </row>
+    <row r="1640">
+      <c r="B1640" s="3" t="n"/>
+    </row>
+    <row r="1641">
+      <c r="B1641" s="3" t="n"/>
+    </row>
+    <row r="1642">
+      <c r="B1642" s="3" t="n"/>
+    </row>
+    <row r="1643">
+      <c r="B1643" s="3" t="n"/>
+    </row>
+    <row r="1644">
+      <c r="B1644" s="3" t="n"/>
+    </row>
+    <row r="1645">
+      <c r="B1645" s="3" t="n"/>
+    </row>
+    <row r="1646">
+      <c r="B1646" s="3" t="n"/>
+    </row>
+    <row r="1647">
+      <c r="B1647" s="3" t="n"/>
+    </row>
+    <row r="1648">
+      <c r="B1648" s="3" t="n"/>
+    </row>
+    <row r="1649">
+      <c r="B1649" s="3" t="n"/>
+    </row>
+    <row r="1650">
+      <c r="B1650" s="3" t="n"/>
+    </row>
+    <row r="1651">
+      <c r="B1651" s="3" t="n"/>
+    </row>
+    <row r="1652">
+      <c r="B1652" s="3" t="n"/>
+    </row>
+    <row r="1653">
+      <c r="B1653" s="3" t="n"/>
+    </row>
+    <row r="1654">
+      <c r="B1654" s="3" t="n"/>
+    </row>
+    <row r="1655">
+      <c r="B1655" s="3" t="n"/>
+    </row>
+    <row r="1656">
+      <c r="B1656" s="3" t="n"/>
+    </row>
+    <row r="1657">
+      <c r="B1657" s="3" t="n"/>
+    </row>
+    <row r="1658">
+      <c r="B1658" s="3" t="n"/>
+    </row>
+    <row r="1659">
+      <c r="B1659" s="3" t="n"/>
+    </row>
+    <row r="1660">
+      <c r="B1660" s="3" t="n"/>
+    </row>
+    <row r="1661">
+      <c r="B1661" s="3" t="n"/>
+    </row>
+    <row r="1662">
+      <c r="B1662" s="3" t="n"/>
+    </row>
+    <row r="1663">
+      <c r="B1663" s="3" t="n"/>
+    </row>
+    <row r="1664">
+      <c r="B1664" s="3" t="n"/>
+    </row>
+    <row r="1665">
+      <c r="B1665" s="3" t="n"/>
+    </row>
+    <row r="1666">
+      <c r="B1666" s="3" t="n"/>
+    </row>
+    <row r="1667">
+      <c r="B1667" s="3" t="n"/>
+    </row>
+    <row r="1668">
+      <c r="B1668" s="3" t="n"/>
+    </row>
+    <row r="1669">
+      <c r="B1669" s="3" t="n"/>
+    </row>
+    <row r="1670">
+      <c r="B1670" s="3" t="n"/>
+    </row>
+    <row r="1671">
+      <c r="B1671" s="3" t="n"/>
+    </row>
+    <row r="1672">
+      <c r="B1672" s="3" t="n"/>
+    </row>
+    <row r="1673">
+      <c r="B1673" s="3" t="n"/>
+    </row>
+    <row r="1674">
+      <c r="B1674" s="3" t="n"/>
+    </row>
+    <row r="1675">
+      <c r="B1675" s="3" t="n"/>
+    </row>
+    <row r="1676">
+      <c r="B1676" s="3" t="n"/>
+    </row>
+    <row r="1677">
+      <c r="B1677" s="3" t="n"/>
+    </row>
+    <row r="1678">
+      <c r="B1678" s="3" t="n"/>
+    </row>
+    <row r="1679">
+      <c r="B1679" s="3" t="n"/>
+    </row>
+    <row r="1680">
+      <c r="B1680" s="3" t="n"/>
+    </row>
+    <row r="1681">
+      <c r="B1681" s="3" t="n"/>
+    </row>
+    <row r="1682">
+      <c r="B1682" s="3" t="n"/>
+    </row>
+    <row r="1683">
+      <c r="B1683" s="3" t="n"/>
+    </row>
+    <row r="1684">
+      <c r="B1684" s="3" t="n"/>
+    </row>
+    <row r="1685">
+      <c r="B1685" s="3" t="n"/>
+    </row>
+    <row r="1686">
+      <c r="B1686" s="3" t="n"/>
+    </row>
+    <row r="1687">
+      <c r="B1687" s="3" t="n"/>
+    </row>
+    <row r="1688">
+      <c r="B1688" s="3" t="n"/>
+    </row>
+    <row r="1689">
+      <c r="B1689" s="3" t="n"/>
+    </row>
+    <row r="1690">
+      <c r="B1690" s="3" t="n"/>
+    </row>
+    <row r="1691">
+      <c r="B1691" s="3" t="n"/>
+    </row>
+    <row r="1692">
+      <c r="B1692" s="3" t="n"/>
+    </row>
+    <row r="1693">
+      <c r="B1693" s="3" t="n"/>
+    </row>
+    <row r="1694">
+      <c r="B1694" s="3" t="n"/>
+    </row>
+    <row r="1695">
+      <c r="B1695" s="3" t="n"/>
+    </row>
+    <row r="1696">
+      <c r="B1696" s="3" t="n"/>
+    </row>
+    <row r="1697">
+      <c r="B1697" s="3" t="n"/>
+    </row>
+    <row r="1698">
+      <c r="B1698" s="3" t="n"/>
+    </row>
+    <row r="1699">
+      <c r="B1699" s="3" t="n"/>
+    </row>
+    <row r="1700">
+      <c r="B1700" s="3" t="n"/>
+    </row>
+    <row r="1701">
+      <c r="B1701" s="3" t="n"/>
+    </row>
+    <row r="1702">
+      <c r="B1702" s="3" t="n"/>
+    </row>
+    <row r="1703">
+      <c r="B1703" s="3" t="n"/>
+    </row>
+    <row r="1704">
+      <c r="B1704" s="3" t="n"/>
+    </row>
+    <row r="1705">
+      <c r="B1705" s="3" t="n"/>
+    </row>
+    <row r="1706">
+      <c r="B1706" s="3" t="n"/>
+    </row>
+    <row r="1707">
+      <c r="B1707" s="3" t="n"/>
+    </row>
+    <row r="1708">
+      <c r="B1708" s="3" t="n"/>
+    </row>
+    <row r="1709">
+      <c r="B1709" s="3" t="n"/>
+    </row>
+    <row r="1710">
+      <c r="B1710" s="3" t="n"/>
+    </row>
+    <row r="1711">
+      <c r="B1711" s="3" t="n"/>
+    </row>
+    <row r="1712">
+      <c r="B1712" s="3" t="n"/>
+    </row>
+    <row r="1713">
+      <c r="B1713" s="3" t="n"/>
+    </row>
+    <row r="1714">
+      <c r="B1714" s="3" t="n"/>
+    </row>
+    <row r="1715">
+      <c r="B1715" s="3" t="n"/>
+    </row>
+    <row r="1716">
+      <c r="B1716" s="3" t="n"/>
+    </row>
+    <row r="1717">
+      <c r="B1717" s="3" t="n"/>
+    </row>
+    <row r="1718">
+      <c r="B1718" s="3" t="n"/>
+    </row>
+    <row r="1719">
+      <c r="B1719" s="3" t="n"/>
+    </row>
+    <row r="1720">
+      <c r="B1720" s="3" t="n"/>
+    </row>
+    <row r="1721">
+      <c r="B1721" s="3" t="n"/>
+    </row>
+    <row r="1722">
+      <c r="B1722" s="3" t="n"/>
+    </row>
+    <row r="1723">
+      <c r="B1723" s="3" t="n"/>
+    </row>
+    <row r="1724">
+      <c r="B1724" s="3" t="n"/>
+    </row>
+    <row r="1725">
+      <c r="B1725" s="3" t="n"/>
+    </row>
+    <row r="1726">
+      <c r="B1726" s="3" t="n"/>
+    </row>
+    <row r="1727">
+      <c r="B1727" s="3" t="n"/>
+    </row>
+    <row r="1728">
+      <c r="B1728" s="3" t="n"/>
+    </row>
+    <row r="1729">
+      <c r="B1729" s="3" t="n"/>
+    </row>
+    <row r="1730">
+      <c r="B1730" s="3" t="n"/>
+    </row>
+    <row r="1731">
+      <c r="B1731" s="3" t="n"/>
+    </row>
+    <row r="1732">
+      <c r="B1732" s="3" t="n"/>
+    </row>
+    <row r="1733">
+      <c r="B1733" s="3" t="n"/>
+    </row>
+    <row r="1734">
+      <c r="B1734" s="3" t="n"/>
+    </row>
+    <row r="1735">
+      <c r="B1735" s="3" t="n"/>
+    </row>
+    <row r="1736">
+      <c r="B1736" s="3" t="n"/>
+    </row>
+    <row r="1737">
+      <c r="B1737" s="3" t="n"/>
+    </row>
+    <row r="1738">
+      <c r="B1738" s="3" t="n"/>
+    </row>
+    <row r="1739">
+      <c r="B1739" s="3" t="n"/>
+    </row>
+    <row r="1740">
+      <c r="B1740" s="3" t="n"/>
+    </row>
+    <row r="1741">
+      <c r="B1741" s="3" t="n"/>
+    </row>
+    <row r="1742">
+      <c r="B1742" s="3" t="n"/>
+    </row>
+    <row r="1743">
+      <c r="B1743" s="3" t="n"/>
+    </row>
+    <row r="1744">
+      <c r="B1744" s="3" t="n"/>
+    </row>
+    <row r="1745">
+      <c r="B1745" s="3" t="n"/>
+    </row>
+    <row r="1746">
+      <c r="B1746" s="3" t="n"/>
+    </row>
+    <row r="1747">
+      <c r="B1747" s="3" t="n"/>
+    </row>
+    <row r="1748">
+      <c r="B1748" s="3" t="n"/>
+    </row>
+    <row r="1749">
+      <c r="B1749" s="3" t="n"/>
+    </row>
+    <row r="1750">
+      <c r="B1750" s="3" t="n"/>
+    </row>
+    <row r="1751">
+      <c r="B1751" s="3" t="n"/>
+    </row>
+    <row r="1752">
+      <c r="B1752" s="3" t="n"/>
+    </row>
+    <row r="1753">
+      <c r="B1753" s="3" t="n"/>
+    </row>
+    <row r="1754">
+      <c r="B1754" s="3" t="n"/>
+    </row>
+    <row r="1755">
+      <c r="B1755" s="3" t="n"/>
+    </row>
+    <row r="1756">
+      <c r="B1756" s="3" t="n"/>
+    </row>
+    <row r="1757">
+      <c r="B1757" s="3" t="n"/>
+    </row>
+    <row r="1758">
+      <c r="B1758" s="3" t="n"/>
+    </row>
+    <row r="1759">
+      <c r="B1759" s="3" t="n"/>
+    </row>
+    <row r="1760">
+      <c r="B1760" s="3" t="n"/>
+    </row>
+    <row r="1761">
+      <c r="B1761" s="3" t="n"/>
+    </row>
+    <row r="1762">
+      <c r="B1762" s="3" t="n"/>
+    </row>
+    <row r="1763">
+      <c r="B1763" s="3" t="n"/>
+    </row>
+    <row r="1764">
+      <c r="B1764" s="3" t="n"/>
+    </row>
+    <row r="1765">
+      <c r="B1765" s="3" t="n"/>
+    </row>
+    <row r="1766">
+      <c r="B1766" s="3" t="n"/>
+    </row>
+    <row r="1767">
+      <c r="B1767" s="3" t="n"/>
+    </row>
+    <row r="1768">
+      <c r="B1768" s="3" t="n"/>
+    </row>
+    <row r="1769">
+      <c r="B1769" s="3" t="n"/>
+    </row>
+    <row r="1770">
+      <c r="B1770" s="3" t="n"/>
+    </row>
+    <row r="1771">
+      <c r="B1771" s="3" t="n"/>
+    </row>
+    <row r="1772">
+      <c r="B1772" s="3" t="n"/>
+    </row>
+    <row r="1773">
+      <c r="B1773" s="3" t="n"/>
+    </row>
+    <row r="1774">
+      <c r="B1774" s="3" t="n"/>
+    </row>
+    <row r="1775">
+      <c r="B1775" s="3" t="n"/>
+    </row>
+    <row r="1776">
+      <c r="B1776" s="3" t="n"/>
+    </row>
+    <row r="1777">
+      <c r="B1777" s="3" t="n"/>
+    </row>
+    <row r="1778">
+      <c r="B1778" s="3" t="n"/>
+    </row>
+    <row r="1779">
+      <c r="B1779" s="3" t="n"/>
+    </row>
+    <row r="1780">
+      <c r="B1780" s="3" t="n"/>
+    </row>
+    <row r="1781">
+      <c r="B1781" s="3" t="n"/>
+    </row>
+    <row r="1782">
+      <c r="B1782" s="3" t="n"/>
+    </row>
+    <row r="1783">
+      <c r="B1783" s="3" t="n"/>
+    </row>
+    <row r="1784">
+      <c r="B1784" s="3" t="n"/>
+    </row>
+    <row r="1785">
+      <c r="B1785" s="3" t="n"/>
+    </row>
+    <row r="1786">
+      <c r="B1786" s="3" t="n"/>
+    </row>
+    <row r="1787">
+      <c r="B1787" s="3" t="n"/>
+    </row>
+    <row r="1788">
+      <c r="B1788" s="3" t="n"/>
+    </row>
+    <row r="1789">
+      <c r="B1789" s="3" t="n"/>
+    </row>
+    <row r="1790">
+      <c r="B1790" s="3" t="n"/>
+    </row>
+    <row r="1791">
+      <c r="B1791" s="3" t="n"/>
+    </row>
+    <row r="1792">
+      <c r="B1792" s="3" t="n"/>
+    </row>
+    <row r="1793">
+      <c r="B1793" s="3" t="n"/>
+    </row>
+    <row r="1794">
+      <c r="B1794" s="3" t="n"/>
+    </row>
+    <row r="1795">
+      <c r="B1795" s="3" t="n"/>
+    </row>
+    <row r="1796">
+      <c r="B1796" s="3" t="n"/>
+    </row>
+    <row r="1797">
+      <c r="B1797" s="3" t="n"/>
+    </row>
+    <row r="1798">
+      <c r="B1798" s="3" t="n"/>
+    </row>
+    <row r="1799">
+      <c r="B1799" s="3" t="n"/>
+    </row>
+    <row r="1800">
+      <c r="B1800" s="3" t="n"/>
+    </row>
+    <row r="1801">
+      <c r="B1801" s="3" t="n"/>
+    </row>
+    <row r="1802">
+      <c r="B1802" s="3" t="n"/>
+    </row>
+    <row r="1803">
+      <c r="B1803" s="3" t="n"/>
+    </row>
+    <row r="1804">
+      <c r="B1804" s="3" t="n"/>
+    </row>
+    <row r="1805">
+      <c r="B1805" s="3" t="n"/>
+    </row>
+    <row r="1806">
+      <c r="B1806" s="3" t="n"/>
+    </row>
+    <row r="1807">
+      <c r="B1807" s="3" t="n"/>
+    </row>
+    <row r="1808">
+      <c r="B1808" s="3" t="n"/>
+    </row>
+    <row r="1809">
+      <c r="B1809" s="3" t="n"/>
+    </row>
+    <row r="1810">
+      <c r="B1810" s="3" t="n"/>
+    </row>
+    <row r="1811">
+      <c r="B1811" s="3" t="n"/>
+    </row>
+    <row r="1812">
+      <c r="B1812" s="3" t="n"/>
+    </row>
+    <row r="1813">
+      <c r="B1813" s="3" t="n"/>
+    </row>
+    <row r="1814">
+      <c r="B1814" s="3" t="n"/>
+    </row>
+    <row r="1815">
+      <c r="B1815" s="3" t="n"/>
+    </row>
+    <row r="1816">
+      <c r="B1816" s="3" t="n"/>
+    </row>
+    <row r="1817">
+      <c r="B1817" s="3" t="n"/>
+    </row>
+    <row r="1818">
+      <c r="B1818" s="3" t="n"/>
+    </row>
+    <row r="1819">
+      <c r="B1819" s="3" t="n"/>
+    </row>
+    <row r="1820">
+      <c r="B1820" s="3" t="n"/>
+    </row>
+    <row r="1821">
+      <c r="B1821" s="3" t="n"/>
+    </row>
+    <row r="1822">
+      <c r="B1822" s="3" t="n"/>
+    </row>
+    <row r="1823">
+      <c r="B1823" s="3" t="n"/>
+    </row>
+    <row r="1824">
+      <c r="B1824" s="3" t="n"/>
+    </row>
+    <row r="1825">
+      <c r="B1825" s="3" t="n"/>
+    </row>
+    <row r="1826">
+      <c r="B1826" s="3" t="n"/>
+    </row>
+    <row r="1827">
+      <c r="B1827" s="3" t="n"/>
+    </row>
+    <row r="1828">
+      <c r="B1828" s="3" t="n"/>
+    </row>
+    <row r="1829">
+      <c r="B1829" s="3" t="n"/>
+    </row>
+    <row r="1830">
+      <c r="B1830" s="3" t="n"/>
+    </row>
+    <row r="1831">
+      <c r="B1831" s="3" t="n"/>
+    </row>
+    <row r="1832">
+      <c r="B1832" s="3" t="n"/>
+    </row>
+    <row r="1833">
+      <c r="B1833" s="3" t="n"/>
+    </row>
+    <row r="1834">
+      <c r="B1834" s="3" t="n"/>
+    </row>
+    <row r="1835">
+      <c r="B1835" s="3" t="n"/>
+    </row>
+    <row r="1836">
+      <c r="B1836" s="3" t="n"/>
+    </row>
+    <row r="1837">
+      <c r="B1837" s="3" t="n"/>
+    </row>
+    <row r="1838">
+      <c r="B1838" s="3" t="n"/>
+    </row>
+    <row r="1839">
+      <c r="B1839" s="3" t="n"/>
+    </row>
+    <row r="1840">
+      <c r="B1840" s="3" t="n"/>
+    </row>
+    <row r="1841">
+      <c r="B1841" s="3" t="n"/>
+    </row>
+    <row r="1842">
+      <c r="B1842" s="3" t="n"/>
+    </row>
+    <row r="1843">
+      <c r="B1843" s="3" t="n"/>
+    </row>
+    <row r="1844">
+      <c r="B1844" s="3" t="n"/>
+    </row>
+    <row r="1845">
+      <c r="B1845" s="3" t="n"/>
+    </row>
+    <row r="1846">
+      <c r="B1846" s="3" t="n"/>
+    </row>
+    <row r="1847">
+      <c r="B1847" s="3" t="n"/>
+    </row>
+    <row r="1848">
+      <c r="B1848" s="3" t="n"/>
+    </row>
+    <row r="1849">
+      <c r="B1849" s="3" t="n"/>
+    </row>
+    <row r="1850">
+      <c r="B1850" s="3" t="n"/>
+    </row>
+    <row r="1851">
+      <c r="B1851" s="3" t="n"/>
+    </row>
+    <row r="1852">
+      <c r="B1852" s="3" t="n"/>
+    </row>
+    <row r="1853">
+      <c r="B1853" s="3" t="n"/>
+    </row>
+    <row r="1854">
+      <c r="B1854" s="3" t="n"/>
+    </row>
+    <row r="1855">
+      <c r="B1855" s="3" t="n"/>
+    </row>
+    <row r="1856">
+      <c r="B1856" s="3" t="n"/>
+    </row>
+    <row r="1857">
+      <c r="B1857" s="3" t="n"/>
+    </row>
+    <row r="1858">
+      <c r="B1858" s="3" t="n"/>
+    </row>
+    <row r="1859">
+      <c r="B1859" s="3" t="n"/>
+    </row>
+    <row r="1860">
+      <c r="B1860" s="3" t="n"/>
+    </row>
+    <row r="1861">
+      <c r="B1861" s="3" t="n"/>
+    </row>
+    <row r="1862">
+      <c r="B1862" s="3" t="n"/>
+    </row>
+    <row r="1863">
+      <c r="B1863" s="3" t="n"/>
+    </row>
+    <row r="1864">
+      <c r="B1864" s="3" t="n"/>
+    </row>
+    <row r="1865">
+      <c r="B1865" s="3" t="n"/>
+    </row>
+    <row r="1866">
+      <c r="B1866" s="3" t="n"/>
+    </row>
+    <row r="1867">
+      <c r="B1867" s="3" t="n"/>
+    </row>
+    <row r="1868">
+      <c r="B1868" s="3" t="n"/>
+    </row>
+    <row r="1869">
+      <c r="B1869" s="3" t="n"/>
+    </row>
+    <row r="1870">
+      <c r="B1870" s="3" t="n"/>
+    </row>
+    <row r="1871">
+      <c r="B1871" s="3" t="n"/>
+    </row>
+    <row r="1872">
+      <c r="B1872" s="3" t="n"/>
+    </row>
+    <row r="1873">
+      <c r="B1873" s="3" t="n"/>
+    </row>
+    <row r="1874">
+      <c r="B1874" s="3" t="n"/>
+    </row>
+    <row r="1875">
+      <c r="B1875" s="3" t="n"/>
+    </row>
+    <row r="1876">
+      <c r="B1876" s="3" t="n"/>
+    </row>
+    <row r="1877">
+      <c r="B1877" s="3" t="n"/>
+    </row>
+    <row r="1878">
+      <c r="B1878" s="3" t="n"/>
+    </row>
+    <row r="1879">
+      <c r="B1879" s="3" t="n"/>
+    </row>
+    <row r="1880">
+      <c r="B1880" s="3" t="n"/>
+    </row>
+    <row r="1881">
+      <c r="B1881" s="3" t="n"/>
+    </row>
+    <row r="1882">
+      <c r="B1882" s="3" t="n"/>
+    </row>
+    <row r="1883">
+      <c r="B1883" s="3" t="n"/>
+    </row>
+    <row r="1884">
+      <c r="B1884" s="3" t="n"/>
+    </row>
+    <row r="1885">
+      <c r="B1885" s="3" t="n"/>
+    </row>
+    <row r="1886">
+      <c r="B1886" s="3" t="n"/>
+    </row>
+    <row r="1887">
+      <c r="B1887" s="3" t="n"/>
+    </row>
+    <row r="1888">
+      <c r="B1888" s="3" t="n"/>
+    </row>
+    <row r="1889">
+      <c r="B1889" s="3" t="n"/>
+    </row>
+    <row r="1890">
+      <c r="B1890" s="3" t="n"/>
+    </row>
+    <row r="1891">
+      <c r="B1891" s="3" t="n"/>
+    </row>
+    <row r="1892">
+      <c r="B1892" s="3" t="n"/>
+    </row>
+    <row r="1893">
+      <c r="B1893" s="3" t="n"/>
+    </row>
+    <row r="1894">
+      <c r="B1894" s="3" t="n"/>
+    </row>
+    <row r="1895">
+      <c r="B1895" s="3" t="n"/>
+    </row>
+    <row r="1896">
+      <c r="B1896" s="3" t="n"/>
+    </row>
+    <row r="1897">
+      <c r="B1897" s="3" t="n"/>
+    </row>
+    <row r="1898">
+      <c r="B1898" s="3" t="n"/>
+    </row>
+    <row r="1899">
+      <c r="B1899" s="3" t="n"/>
+    </row>
+    <row r="1900">
+      <c r="B1900" s="3" t="n"/>
+    </row>
+    <row r="1901">
+      <c r="B1901" s="3" t="n"/>
+    </row>
+    <row r="1902">
+      <c r="B1902" s="3" t="n"/>
+    </row>
+    <row r="1903">
+      <c r="B1903" s="3" t="n"/>
+    </row>
+    <row r="1904">
+      <c r="B1904" s="3" t="n"/>
+    </row>
+    <row r="1905">
+      <c r="B1905" s="3" t="n"/>
+    </row>
+    <row r="1906">
+      <c r="B1906" s="3" t="n"/>
+    </row>
+    <row r="1907">
+      <c r="B1907" s="3" t="n"/>
+    </row>
+    <row r="1908">
+      <c r="B1908" s="3" t="n"/>
+    </row>
+    <row r="1909">
+      <c r="B1909" s="3" t="n"/>
+    </row>
+    <row r="1910">
+      <c r="B1910" s="3" t="n"/>
+    </row>
+    <row r="1911">
+      <c r="B1911" s="3" t="n"/>
+    </row>
+    <row r="1912">
+      <c r="B1912" s="3" t="n"/>
+    </row>
+    <row r="1913">
+      <c r="B1913" s="3" t="n"/>
+    </row>
+    <row r="1914">
+      <c r="B1914" s="3" t="n"/>
+    </row>
+    <row r="1915">
+      <c r="B1915" s="3" t="n"/>
+    </row>
+    <row r="1916">
+      <c r="B1916" s="3" t="n"/>
+    </row>
+    <row r="1917">
+      <c r="B1917" s="3" t="n"/>
+    </row>
+    <row r="1918">
+      <c r="B1918" s="3" t="n"/>
+    </row>
+    <row r="1919">
+      <c r="B1919" s="3" t="n"/>
+    </row>
+    <row r="1920">
+      <c r="B1920" s="3" t="n"/>
+    </row>
+    <row r="1921">
+      <c r="B1921" s="3" t="n"/>
+    </row>
+    <row r="1922">
+      <c r="B1922" s="3" t="n"/>
+    </row>
+    <row r="1923">
+      <c r="B1923" s="3" t="n"/>
+    </row>
+    <row r="1924">
+      <c r="B1924" s="3" t="n"/>
+    </row>
+    <row r="1925">
+      <c r="B1925" s="3" t="n"/>
+    </row>
+    <row r="1926">
+      <c r="B1926" s="3" t="n"/>
+    </row>
+    <row r="1927">
+      <c r="B1927" s="3" t="n"/>
+    </row>
+    <row r="1928">
+      <c r="B1928" s="3" t="n"/>
+    </row>
+    <row r="1929">
+      <c r="B1929" s="3" t="n"/>
+    </row>
+    <row r="1930">
+      <c r="B1930" s="3" t="n"/>
+    </row>
+    <row r="1931">
+      <c r="B1931" s="3" t="n"/>
+    </row>
+    <row r="1932">
+      <c r="B1932" s="3" t="n"/>
+    </row>
+    <row r="1933">
+      <c r="B1933" s="3" t="n"/>
+    </row>
+    <row r="1934">
+      <c r="B1934" s="3" t="n"/>
+    </row>
+    <row r="1935">
+      <c r="B1935" s="3" t="n"/>
+    </row>
+    <row r="1936">
+      <c r="B1936" s="3" t="n"/>
+    </row>
+    <row r="1937">
+      <c r="B1937" s="3" t="n"/>
+    </row>
+    <row r="1938">
+      <c r="B1938" s="3" t="n"/>
+    </row>
+    <row r="1939">
+      <c r="B1939" s="3" t="n"/>
+    </row>
+    <row r="1940">
+      <c r="B1940" s="3" t="n"/>
+    </row>
+    <row r="1941">
+      <c r="B1941" s="3" t="n"/>
+    </row>
+    <row r="1942">
+      <c r="B1942" s="3" t="n"/>
+    </row>
+    <row r="1943">
+      <c r="B1943" s="3" t="n"/>
+    </row>
+    <row r="1944">
+      <c r="B1944" s="3" t="n"/>
+    </row>
+    <row r="1945">
+      <c r="B1945" s="3" t="n"/>
+    </row>
+    <row r="1946">
+      <c r="B1946" s="3" t="n"/>
+    </row>
+    <row r="1947">
+      <c r="B1947" s="3" t="n"/>
+    </row>
+    <row r="1948">
+      <c r="B1948" s="3" t="n"/>
+    </row>
+    <row r="1949">
+      <c r="B1949" s="3" t="n"/>
+    </row>
+    <row r="1950">
+      <c r="B1950" s="3" t="n"/>
+    </row>
+    <row r="1951">
+      <c r="B1951" s="3" t="n"/>
+    </row>
+    <row r="1952">
+      <c r="B1952" s="3" t="n"/>
+    </row>
+    <row r="1953">
+      <c r="B1953" s="3" t="n"/>
+    </row>
+    <row r="1954">
+      <c r="B1954" s="3" t="n"/>
+    </row>
+    <row r="1955">
+      <c r="B1955" s="3" t="n"/>
+    </row>
+    <row r="1956">
+      <c r="B1956" s="3" t="n"/>
+    </row>
+    <row r="1957">
+      <c r="B1957" s="3" t="n"/>
+    </row>
+    <row r="1958">
+      <c r="B1958" s="3" t="n"/>
+    </row>
+    <row r="1959">
+      <c r="B1959" s="3" t="n"/>
+    </row>
+    <row r="1960">
+      <c r="B1960" s="3" t="n"/>
+    </row>
+    <row r="1961">
+      <c r="B1961" s="3" t="n"/>
+    </row>
+    <row r="1962">
+      <c r="B1962" s="3" t="n"/>
+    </row>
+    <row r="1963">
+      <c r="B1963" s="3" t="n"/>
+    </row>
+    <row r="1964">
+      <c r="B1964" s="3" t="n"/>
+    </row>
+    <row r="1965">
+      <c r="B1965" s="3" t="n"/>
+    </row>
+    <row r="1966">
+      <c r="B1966" s="3" t="n"/>
+    </row>
+    <row r="1967">
+      <c r="B1967" s="3" t="n"/>
+    </row>
+    <row r="1968">
+      <c r="B1968" s="3" t="n"/>
+    </row>
+    <row r="1969">
+      <c r="B1969" s="3" t="n"/>
+    </row>
+    <row r="1970">
+      <c r="B1970" s="3" t="n"/>
+    </row>
+    <row r="1971">
+      <c r="B1971" s="3" t="n"/>
+    </row>
+    <row r="1972">
+      <c r="B1972" s="3" t="n"/>
+    </row>
+    <row r="1973">
+      <c r="B1973" s="3" t="n"/>
+    </row>
+    <row r="1974">
+      <c r="B1974" s="3" t="n"/>
+    </row>
+    <row r="1975">
+      <c r="B1975" s="3" t="n"/>
+    </row>
+    <row r="1976">
+      <c r="B1976" s="3" t="n"/>
+    </row>
+    <row r="1977">
+      <c r="B1977" s="3" t="n"/>
+    </row>
+    <row r="1978">
+      <c r="B1978" s="3" t="n"/>
+    </row>
+    <row r="1979">
+      <c r="B1979" s="3" t="n"/>
+    </row>
+    <row r="1980">
+      <c r="B1980" s="3" t="n"/>
+    </row>
+    <row r="1981">
+      <c r="B1981" s="3" t="n"/>
+    </row>
+    <row r="1982">
+      <c r="B1982" s="3" t="n"/>
+    </row>
+    <row r="1983">
+      <c r="B1983" s="3" t="n"/>
+    </row>
+    <row r="1984">
+      <c r="B1984" s="3" t="n"/>
+    </row>
+    <row r="1985">
+      <c r="B1985" s="3" t="n"/>
+    </row>
+    <row r="1986">
+      <c r="B1986" s="3" t="n"/>
+    </row>
+    <row r="1987">
+      <c r="B1987" s="3" t="n"/>
+    </row>
+    <row r="1988">
+      <c r="B1988" s="3" t="n"/>
+    </row>
+    <row r="1989">
+      <c r="B1989" s="3" t="n"/>
+    </row>
+    <row r="1990">
+      <c r="B1990" s="3" t="n"/>
+    </row>
+    <row r="1991">
+      <c r="B1991" s="3" t="n"/>
+    </row>
+    <row r="1992">
+      <c r="B1992" s="3" t="n"/>
+    </row>
+    <row r="1993">
+      <c r="B1993" s="3" t="n"/>
+    </row>
+    <row r="1994">
+      <c r="B1994" s="3" t="n"/>
+    </row>
+    <row r="1995">
+      <c r="B1995" s="3" t="n"/>
+    </row>
+    <row r="1996">
+      <c r="B1996" s="3" t="n"/>
+    </row>
+    <row r="1997">
+      <c r="B1997" s="3" t="n"/>
+    </row>
+    <row r="1998">
+      <c r="B1998" s="3" t="n"/>
+    </row>
+    <row r="1999">
+      <c r="B1999" s="3" t="n"/>
+    </row>
+    <row r="2000">
+      <c r="B2000" s="3" t="n"/>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>nombre_bot</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>Mermín</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>Nombre con el que se presenta el bot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>nombre_negocio</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>ITS WOOD</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>Nombre del negocio en los mensajes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>tono</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>cercano</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>cercano (tutea) o formal (trata de usted).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>emoji_bot</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>🌳</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>Emoji que acompaña al nombre del bot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>url_web</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr"/>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>Tienda web a la que se redirige en el primer mensaje. Vacío = sin enlace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>codigo_descuento_web</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>WEB10</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>Código de descuento para comprar en la web.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>porcentaje_descuento_web</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>Porcentaje del descuento web (solo el número).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>mensaje_bienvenida</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr"/>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>Plantilla del primer mensaje: {hola}, {nombre_bot}, {emoji_bot}, {nombre_negocio}, {porcentaje}, {codigo}, {url}. Vacío = plantilla del tono.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>drive_folder_id</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr"/>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>Carpeta de Drive con la hoja MERMIN_FUENTE. Se llena desde el dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>sheet_fuente_id</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr"/>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>Hoja fuente detectada por la sincronización.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>ultima_sync</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr"/>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>Fecha de la última sincronización correcta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>margen_por_defecto</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>Margen para productos sin costo (0.40 = 40 %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>umbral_prioridad_alta</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>Puntaje desde el que un lead es ALTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>umbral_prioridad_media</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>Puntaje desde el que un lead es MEDIA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>tope_valor</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>Valor (S/) que cuenta como 100 % en la prioridad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>tope_ganancia</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>Ganancia (S/) que cuenta como 100 % en la prioridad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>tope_cantidad</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>Unidades que cuentan como 100 % en la prioridad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>tfr_antes_minutos</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>Tiempo de primera respuesta antes del bot, en minutos (línea base manual).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>avisos_whatsapp</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr"/>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>WhatsApp que recibe los avisos de leads ALTA (con código de país).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>avisos_email</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr"/>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>Correos que reciben los resúmenes, separados por coma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>hora_resumen_diario</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>Hora del resumen diario (HH:MM, hora de Lima).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/chatbot/hoja/pestanas_bot_itswood.xlsx
+++ b/chatbot/hoja/pestanas_bot_itswood.xlsx
@@ -193,7 +193,7 @@
         <t>El bot la crea en PENDIENTE_HUMANO; después la gestiona el equipo.</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>Columna del equipo: el bot no la escribe.</t>
       </text>
@@ -26124,7 +26124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2000"/>
+  <dimension ref="A1:AD2000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -26152,7 +26152,11 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="23" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="23" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="23" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26281,7 +26285,27 @@
           <t>puntaje_intencion</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>valor_estimado</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ganancia_estimada</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>prioridad</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>puntaje_prioridad</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>notas_equipo</t>
         </is>

--- a/chatbot/hoja/pestanas_bot_itswood.xlsx
+++ b/chatbot/hoja/pestanas_bot_itswood.xlsx
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_PRODUCTOS" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CLIENTES_FUENTE" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_VENTAS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CATALOGO" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_FIDELIZACION" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CATALOGO" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -278,6 +279,21 @@
 </file>
 
 <file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ITS WOOD bot</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional: escribe NO para ocultar el producto al bot.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>ITS WOOD bot</author>
@@ -12801,7 +12817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2000"/>
+  <dimension ref="A1:K2000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12811,6 +12827,10 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12847,6 +12867,26 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acepta_marketing</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>segmento</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>pedidos</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_comprado</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ultima_compra</t>
         </is>
       </c>
     </row>
@@ -18919,6 +18959,221 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>segmento</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mensaje</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>oferta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>frecuencia_dias</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CORPORATIVO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMAIL + ASESOR POR WHATSAPP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hola {nombre}, te compartimos el catálogo corporativo de {negocio}. Para tus próximos regalos te recomendamos {producto}. {oferta}. ¿Agendamos una llamada con un asesor?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Descuento por volumen desde 50 unidades y logo grabado sin costo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WHATSAPP PERSONAL (HUMANO)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Hola {nombre}, eres de nuestros clientes favoritos de {negocio} 🌳 {oferta}. Te separamos {producto} antes que nadie.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Acceso anticipado a la nueva colección y un regalo en tu próximo pedido</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RECURRENTE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PLANTILLA DE WHATSAPP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hola {nombre}, a quienes compraron lo mismo que tú también les encantó {producto}. {oferta} 👉 {url}</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10% de descuento en tu siguiente compra</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EMAIL Y WHATSAPP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>¡Gracias por tu compra, {nombre}! ¿Nos dejas una reseña? Como agradecimiento: {oferta}. Te podría gustar {producto}.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cupón SEGUNDA10 para tu segunda compra</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DORMIDO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>WHATSAPP CON CUPÓN + RETARGETING EN META ADS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hola {nombre}, te extrañamos en {negocio}. Vuelve con {oferta}: {producto} te está esperando 👉 {url}</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cupón VUELVE15 por 15 días</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/chatbot/hoja/pestanas_bot_itswood.xlsx
+++ b/chatbot/hoja/pestanas_bot_itswood.xlsx
@@ -19,7 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CLIENTES_FUENTE" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_VENTAS" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_FIDELIZACION" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CATALOGO" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CAMPANAS" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOT_CATALOGO" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -294,6 +295,21 @@
 </file>
 
 <file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ITS WOOD bot</author>
+  </authors>
+  <commentList>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>El bot la crea en PENDIENTE_HUMANO; después la gestiona el equipo.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>ITS WOOD bot</author>
@@ -19179,6 +19195,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>campana_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>segmento</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>cliente_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>canal</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>destino</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>asunto</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mensaje</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>detalle</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
